--- a/argus/kship/models/460930_model.xlsx
+++ b/argus/kship/models/460930_model.xlsx
@@ -684,25 +684,25 @@
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 266379억 × 비례계수 0.0135 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 266378억 × 비례계수 0.0135 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AB21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 267740억 × 비례계수 0.0135 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 268576억 × 비례계수 0.0135 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 266428억 × 비례계수 0.0135 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 267243억 × 비례계수 0.0135 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 264185억 × 비례계수 0.0135 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 264981억 × 비례계수 0.0135 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="S22" authorId="0" shapeId="0">
@@ -942,7 +942,7 @@
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1111억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1112억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="S26" authorId="0" shapeId="0">
@@ -1731,25 +1731,25 @@
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 266379억 × 비례계수 0.0135 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 266378억 × 비례계수 0.0135 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AB5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 267740억 × 비례계수 0.0135 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 268576억 × 비례계수 0.0135 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 266428억 × 비례계수 0.0135 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 267243억 × 비례계수 0.0135 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 264185억 × 비례계수 0.0135 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 264981억 × 비례계수 0.0135 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2164,7 +2164,7 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1111억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1112억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -5510,13 +5510,13 @@
         <v>0.172635</v>
       </c>
       <c r="AB21" s="24" t="n">
-        <v>0.128218</v>
+        <v>0.131736</v>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.07413</v>
+        <v>0.07742</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.020402</v>
+        <v>0.02347</v>
       </c>
       <c r="AE21" s="25" t="n"/>
     </row>
@@ -5622,13 +5622,13 @@
         <v>0.03759</v>
       </c>
       <c r="AB22" s="24" t="n">
-        <v>0.037596</v>
+        <v>0.037598</v>
       </c>
       <c r="AC22" s="24" t="n">
-        <v>0.037593</v>
+        <v>0.037592</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.037593</v>
+        <v>0.037598</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
@@ -5737,13 +5737,13 @@
         <v>0.118041</v>
       </c>
       <c r="AB23" s="24" t="n">
-        <v>0.118047</v>
+        <v>0.118048</v>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.118048</v>
+        <v>0.118041</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.118041</v>
+        <v>0.11804</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
@@ -6167,13 +6167,13 @@
         <v>0.190627</v>
       </c>
       <c r="AB27" s="24" t="n">
-        <v>0.190626</v>
+        <v>0.190584</v>
       </c>
       <c r="AC27" s="24" t="n">
-        <v>0.190646</v>
+        <v>0.190637</v>
       </c>
       <c r="AD27" s="24" t="n">
-        <v>0.19062</v>
+        <v>0.190578</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE14/subQ!AE13,"")</f>
@@ -6470,16 +6470,16 @@
       </c>
       <c r="Z30" s="30" t="n"/>
       <c r="AA30" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AB30" s="29" t="n">
         <v>46.17</v>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AE30" s="30" t="n"/>
     </row>
@@ -6564,16 +6564,16 @@
       </c>
       <c r="Z31" s="30" t="n"/>
       <c r="AA31" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AB31" s="29" t="n">
         <v>46.17</v>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AE31" s="30" t="n"/>
     </row>
@@ -6809,13 +6809,13 @@
         <v>0.097648</v>
       </c>
       <c r="AB34" s="24" t="n">
-        <v>0.047327</v>
+        <v>0.047614</v>
       </c>
       <c r="AC34" s="24" t="n">
-        <v>0.0863</v>
+        <v>0.086521</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.084646</v>
+        <v>0.08484800000000001</v>
       </c>
       <c r="AE34" s="25" t="n"/>
     </row>
@@ -7263,13 +7263,13 @@
         <v>-0.10143</v>
       </c>
       <c r="AB40" s="24" t="n">
-        <v>-0.14753</v>
+        <v>-0.148198</v>
       </c>
       <c r="AC40" s="24" t="n">
-        <v>-0.131853</v>
+        <v>-0.132547</v>
       </c>
       <c r="AD40" s="24" t="n">
-        <v>-0.097525</v>
+        <v>-0.098981</v>
       </c>
       <c r="AE40" s="25" t="n"/>
     </row>
@@ -7575,13 +7575,13 @@
         <v>0.118041</v>
       </c>
       <c r="AB43" s="24" t="n">
-        <v>0.118047</v>
+        <v>0.118048</v>
       </c>
       <c r="AC43" s="24" t="n">
-        <v>0.118048</v>
+        <v>0.118041</v>
       </c>
       <c r="AD43" s="24" t="n">
-        <v>0.118041</v>
+        <v>0.11804</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE34/subQ!AE33,"")</f>

--- a/argus/kship/models/460930_model.xlsx
+++ b/argus/kship/models/460930_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AE$1</definedName>
     <definedName name="환율">변수!$C$6:$AE$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AE$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AE$87</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AE$94</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AE$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AE$84</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AE$1</definedName>
@@ -678,31 +678,31 @@
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 258903억 × 비례계수 0.0135 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 259912억 × 비례계수 0.0135 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 266378억 × 비례계수 0.0135 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 271175억 × 비례계수 0.0135 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AB21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 268576억 × 비례계수 0.0135 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 281333억 × 비례계수 0.0135 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 267243억 × 비례계수 0.0135 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 293149억 × 비례계수 0.0135 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 264981억 × 비례계수 0.0135 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 308856억 × 비례계수 0.0135 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="S22" authorId="0" shapeId="0">
@@ -930,19 +930,19 @@
     <comment ref="AB25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 977억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 978억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1023억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1029억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1112억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1126억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="S26" authorId="0" shapeId="0">
@@ -1725,31 +1725,31 @@
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 258903억 × 비례계수 0.0135 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 259912억 × 비례계수 0.0135 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 266378억 × 비례계수 0.0135 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 271175억 × 비례계수 0.0135 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AB5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 268576억 × 비례계수 0.0135 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 281333억 × 비례계수 0.0135 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 267243억 × 비례계수 0.0135 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 293149억 × 비례계수 0.0135 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 264981억 × 비례계수 0.0135 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 308856억 × 비례계수 0.0135 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2152,19 +2152,19 @@
     </comment>
     <comment ref="AB11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 977억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 978억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AC11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1023억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1029억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1112억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1126억 × 2.26% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -3845,7 +3845,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 1.5, "op_wape_pct": 19.3, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 612.63, "rev_act": 605.92, "op_pred": 65.82, "op_act": 67.88}, {"q": "2025Q4", "rev_pred": 671.82, "rev_act": 669.42, "op_pred": 72.18, "op_act": 64.77}, {"q": "2026Q1", "rev_pred": 673.26, "rev_act": 646.1, "op_pred": 72.34, "op_act": 85.3}, {"q": "2026Q2", "rev_pred": 731.64, "rev_act": 727.68, "op_pred": 78.61, "op_act": 121.83}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 1.5, "op_wape_pct": 19.3, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": null, "wape_trend": null, "adopted": true, "note": "동결 2024Q2 이전 실적 3분기(&lt;8) 또는 이후 실측 0분기 → OOS 비교 불가, 유의성 조건만으로 채택"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 612.63, "rev_act": 605.92, "op_pred": 65.82, "op_act": 67.88}, {"q": "2025Q4", "rev_pred": 671.82, "rev_act": 669.42, "op_pred": 72.18, "op_act": 64.77}, {"q": "2026Q1", "rev_pred": 673.26, "rev_act": 646.1, "op_pred": 72.34, "op_act": 85.3}, {"q": "2026Q2", "rev_pred": 731.64, "rev_act": 727.68, "op_pred": 78.61, "op_act": 121.83}]}</t>
         </is>
       </c>
     </row>
@@ -5503,20 +5503,20 @@
         <v>0.161211</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.190046</v>
+        <v>0.194688</v>
       </c>
       <c r="Z21" s="25" t="n"/>
       <c r="AA21" s="24" t="n">
-        <v>0.172635</v>
+        <v>0.193755</v>
       </c>
       <c r="AB21" s="24" t="n">
-        <v>0.131736</v>
+        <v>0.185493</v>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.07742</v>
+        <v>0.181849</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.02347</v>
+        <v>0.188304</v>
       </c>
       <c r="AE21" s="25" t="n"/>
     </row>
@@ -5612,23 +5612,23 @@
         <v>0.037593</v>
       </c>
       <c r="Y22" s="24" t="n">
-        <v>0.037593</v>
+        <v>0.037589</v>
       </c>
       <c r="Z22" s="25">
         <f>IFERROR(subQ!Z8/subQ!Z5,"")</f>
         <v/>
       </c>
       <c r="AA22" s="24" t="n">
-        <v>0.03759</v>
+        <v>0.037593</v>
       </c>
       <c r="AB22" s="24" t="n">
-        <v>0.037598</v>
+        <v>0.037589</v>
       </c>
       <c r="AC22" s="24" t="n">
-        <v>0.037592</v>
+        <v>0.037595</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.037598</v>
+        <v>0.037593</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
@@ -5734,16 +5734,16 @@
         <v/>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.118041</v>
+        <v>0.118038</v>
       </c>
       <c r="AB23" s="24" t="n">
-        <v>0.118048</v>
+        <v>0.118042</v>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.118041</v>
+        <v>0.11804</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.11804</v>
+        <v>0.118043</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
@@ -5937,13 +5937,13 @@
         <v>5.02</v>
       </c>
       <c r="AB25" s="29" t="n">
-        <v>5.51</v>
+        <v>5.52</v>
       </c>
       <c r="AC25" s="29" t="n">
-        <v>5.77</v>
+        <v>5.81</v>
       </c>
       <c r="AD25" s="29" t="n">
-        <v>6.27</v>
+        <v>6.35</v>
       </c>
       <c r="AE25" s="30">
         <f>subQ!AE11</f>
@@ -6157,23 +6157,23 @@
         <v>0.190619</v>
       </c>
       <c r="Y27" s="24" t="n">
-        <v>0.190574</v>
+        <v>0.190573</v>
       </c>
       <c r="Z27" s="25">
         <f>IFERROR(subQ!Z14/subQ!Z13,"")</f>
         <v/>
       </c>
       <c r="AA27" s="24" t="n">
-        <v>0.190627</v>
+        <v>0.190603</v>
       </c>
       <c r="AB27" s="24" t="n">
-        <v>0.190584</v>
+        <v>0.190608</v>
       </c>
       <c r="AC27" s="24" t="n">
-        <v>0.190637</v>
+        <v>0.19064</v>
       </c>
       <c r="AD27" s="24" t="n">
-        <v>0.190578</v>
+        <v>0.190614</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE14/subQ!AE13,"")</f>
@@ -6470,16 +6470,16 @@
       </c>
       <c r="Z30" s="30" t="n"/>
       <c r="AA30" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AB30" s="29" t="n">
-        <v>46.17</v>
+        <v>46.16</v>
       </c>
       <c r="AC30" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AD30" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AD30" s="29" t="n">
-        <v>0.01</v>
       </c>
       <c r="AE30" s="30" t="n"/>
     </row>
@@ -6564,16 +6564,16 @@
       </c>
       <c r="Z31" s="30" t="n"/>
       <c r="AA31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AB31" s="29" t="n">
-        <v>46.17</v>
+        <v>46.16</v>
       </c>
       <c r="AC31" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AD31" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AD31" s="29" t="n">
-        <v>0.01</v>
       </c>
       <c r="AE31" s="30" t="n"/>
     </row>
@@ -6802,20 +6802,20 @@
         <v>0.112987</v>
       </c>
       <c r="Y34" s="24" t="n">
-        <v>0.113722</v>
+        <v>0.114147</v>
       </c>
       <c r="Z34" s="25" t="n"/>
       <c r="AA34" s="24" t="n">
-        <v>0.097648</v>
+        <v>0.099284</v>
       </c>
       <c r="AB34" s="24" t="n">
-        <v>0.047614</v>
+        <v>0.051817</v>
       </c>
       <c r="AC34" s="24" t="n">
-        <v>0.086521</v>
+        <v>0.093933</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.08484800000000001</v>
+        <v>0.09697</v>
       </c>
       <c r="AE34" s="25" t="n"/>
     </row>
@@ -7256,20 +7256,20 @@
         <v>-0.139701</v>
       </c>
       <c r="Y40" s="24" t="n">
-        <v>-0.08885899999999999</v>
+        <v>-0.08952300000000001</v>
       </c>
       <c r="Z40" s="25" t="n"/>
       <c r="AA40" s="24" t="n">
-        <v>-0.10143</v>
+        <v>-0.106875</v>
       </c>
       <c r="AB40" s="24" t="n">
-        <v>-0.148198</v>
+        <v>-0.162884</v>
       </c>
       <c r="AC40" s="24" t="n">
-        <v>-0.132547</v>
+        <v>-0.165857</v>
       </c>
       <c r="AD40" s="24" t="n">
-        <v>-0.098981</v>
+        <v>-0.164603</v>
       </c>
       <c r="AE40" s="25" t="n"/>
     </row>
@@ -7345,16 +7345,16 @@
       </c>
       <c r="Z41" s="25" t="n"/>
       <c r="AA41" s="24" t="n">
-        <v>-0.089172</v>
+        <v>-0.095541</v>
       </c>
       <c r="AB41" s="24" t="n">
         <v>-0.096774</v>
       </c>
       <c r="AC41" s="24" t="n">
-        <v>-0.09271500000000001</v>
+        <v>-0.099338</v>
       </c>
       <c r="AD41" s="24" t="n">
-        <v>-0.095238</v>
+        <v>-0.102041</v>
       </c>
       <c r="AE41" s="25" t="n"/>
     </row>
@@ -7572,16 +7572,16 @@
         <v/>
       </c>
       <c r="AA43" s="24" t="n">
-        <v>0.118041</v>
+        <v>0.118038</v>
       </c>
       <c r="AB43" s="24" t="n">
-        <v>0.118048</v>
+        <v>0.118042</v>
       </c>
       <c r="AC43" s="24" t="n">
-        <v>0.118041</v>
+        <v>0.11804</v>
       </c>
       <c r="AD43" s="24" t="n">
-        <v>0.11804</v>
+        <v>0.118043</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE34/subQ!AE33,"")</f>
@@ -8050,7 +8050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE87"/>
+  <dimension ref="A1:AE94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -12481,48 +12481,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E72" s="18" t="n">
-        <v>2314.46</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F72" s="9" t="n"/>
-      <c r="G72" s="18" t="n">
-        <v>2688.39</v>
-      </c>
-      <c r="H72" s="18" t="n">
-        <v>15647.19</v>
-      </c>
-      <c r="I72" s="18" t="n">
-        <v>2938.3</v>
-      </c>
-      <c r="J72" s="18" t="n">
-        <v>10103.9</v>
-      </c>
-      <c r="K72" s="34" t="n">
-        <v>31377.78</v>
-      </c>
-      <c r="L72" s="18" t="n">
-        <v>10071.76</v>
-      </c>
-      <c r="M72" s="18" t="n">
-        <v>7964.27</v>
-      </c>
-      <c r="N72" s="18" t="n">
-        <v>12079.76</v>
-      </c>
-      <c r="O72" s="18" t="n">
-        <v>6901.99</v>
-      </c>
-      <c r="P72" s="34" t="n">
-        <v>37017.78</v>
-      </c>
-      <c r="Q72" s="18" t="n">
-        <v>8954.08</v>
-      </c>
+      <c r="K72" s="9" t="n"/>
+      <c r="P72" s="9" t="n"/>
       <c r="R72" s="19" t="n">
-        <v>10475.1</v>
+        <v>221.42</v>
       </c>
       <c r="S72" s="10" t="n"/>
       <c r="T72" s="10" t="n"/>
@@ -12544,48 +12510,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="E73" s="18" t="n">
-        <v>40.76</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F73" s="9" t="n"/>
-      <c r="G73" s="18" t="n">
-        <v>110.88</v>
-      </c>
-      <c r="H73" s="18" t="n">
-        <v>268.43</v>
-      </c>
-      <c r="I73" s="18" t="n">
-        <v>752.84</v>
-      </c>
-      <c r="J73" s="18" t="n">
-        <v>244.72</v>
-      </c>
-      <c r="K73" s="34" t="n">
-        <v>1376.87</v>
-      </c>
-      <c r="L73" s="18" t="n">
-        <v>249.93</v>
-      </c>
-      <c r="M73" s="18" t="n">
-        <v>154.91</v>
-      </c>
-      <c r="N73" s="18" t="n">
-        <v>284.67</v>
-      </c>
-      <c r="O73" s="18" t="n">
-        <v>200.48</v>
-      </c>
-      <c r="P73" s="34" t="n">
-        <v>889.99</v>
-      </c>
-      <c r="Q73" s="18" t="n">
-        <v>276.05</v>
-      </c>
+      <c r="K73" s="9" t="n"/>
+      <c r="P73" s="9" t="n"/>
       <c r="R73" s="19" t="n">
-        <v>208.22</v>
+        <v>206.32</v>
       </c>
       <c r="S73" s="10" t="n"/>
       <c r="T73" s="10" t="n"/>
@@ -12607,48 +12539,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E74" s="18" t="n">
-        <v>-492.18</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F74" s="9" t="n"/>
-      <c r="G74" s="18" t="n">
-        <v>-169.27</v>
-      </c>
-      <c r="H74" s="18" t="n">
-        <v>-981.99</v>
-      </c>
-      <c r="I74" s="18" t="n">
-        <v>-695.25</v>
-      </c>
-      <c r="J74" s="18" t="n">
-        <v>-248.75</v>
-      </c>
-      <c r="K74" s="34" t="n">
-        <v>-2095.26</v>
-      </c>
-      <c r="L74" s="18" t="n">
-        <v>-664.97</v>
-      </c>
-      <c r="M74" s="18" t="n">
-        <v>-830.21</v>
-      </c>
-      <c r="N74" s="18" t="n">
-        <v>-904.71</v>
-      </c>
-      <c r="O74" s="18" t="n">
-        <v>-44.36</v>
-      </c>
-      <c r="P74" s="34" t="n">
-        <v>-2444.25</v>
-      </c>
-      <c r="Q74" s="18" t="n">
-        <v>-1927.77</v>
-      </c>
+      <c r="K74" s="9" t="n"/>
+      <c r="P74" s="9" t="n"/>
       <c r="R74" s="19" t="n">
-        <v>-2388.87</v>
+        <v>4.78</v>
       </c>
       <c r="S74" s="10" t="n"/>
       <c r="T74" s="10" t="n"/>
@@ -12670,48 +12568,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E75" s="18" t="n">
-        <v>-5324.78</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F75" s="9" t="n"/>
-      <c r="G75" s="18" t="n">
-        <v>-22956.9</v>
-      </c>
-      <c r="H75" s="18" t="n">
-        <v>1960.95</v>
-      </c>
-      <c r="I75" s="18" t="n">
-        <v>-10774.79</v>
-      </c>
-      <c r="J75" s="18" t="n">
-        <v>1360.91</v>
-      </c>
-      <c r="K75" s="34" t="n">
-        <v>-30409.83</v>
-      </c>
-      <c r="L75" s="18" t="n">
-        <v>-1050</v>
-      </c>
-      <c r="M75" s="18" t="n">
-        <v>-11463.3</v>
-      </c>
-      <c r="N75" s="18" t="n">
-        <v>-7046.15</v>
-      </c>
-      <c r="O75" s="18" t="n">
-        <v>2301.1</v>
-      </c>
-      <c r="P75" s="34" t="n">
-        <v>-17258.35</v>
-      </c>
-      <c r="Q75" s="18" t="n">
-        <v>6919.52</v>
-      </c>
+      <c r="K75" s="9" t="n"/>
+      <c r="P75" s="9" t="n"/>
       <c r="R75" s="19" t="n">
-        <v>-6399.3</v>
+        <v>6.46</v>
       </c>
       <c r="S75" s="10" t="n"/>
       <c r="T75" s="10" t="n"/>
@@ -12733,39 +12597,15 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E76" s="18" t="n">
-        <v>4928.9</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F76" s="9" t="n"/>
-      <c r="G76" s="18" t="n">
-        <v>1386.73</v>
-      </c>
-      <c r="H76" s="18" t="n">
-        <v>1391.09</v>
-      </c>
-      <c r="I76" s="18" t="n">
-        <v>4903.72</v>
-      </c>
-      <c r="J76" s="18" t="n">
-        <v>3382.74</v>
-      </c>
-      <c r="K76" s="34" t="n">
-        <v>11064.28</v>
-      </c>
-      <c r="L76" s="18" t="n">
-        <v>1076.04</v>
-      </c>
-      <c r="M76" s="18" t="n">
-        <v>5491.14</v>
-      </c>
-      <c r="N76" s="18" t="n">
-        <v>3141.15</v>
-      </c>
+      <c r="K76" s="9" t="n"/>
       <c r="P76" s="9" t="n"/>
-      <c r="R76" s="5" t="n"/>
+      <c r="R76" s="19" t="n">
+        <v>-2.17</v>
+      </c>
       <c r="S76" s="10" t="n"/>
       <c r="T76" s="10" t="n"/>
       <c r="U76" s="11" t="n"/>
@@ -12786,39 +12626,15 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E77" s="18" t="n">
-        <v>4933.4</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F77" s="9" t="n"/>
-      <c r="G77" s="18" t="n">
-        <v>1386.73</v>
-      </c>
-      <c r="H77" s="18" t="n">
-        <v>1391.09</v>
-      </c>
-      <c r="I77" s="18" t="n">
-        <v>4920.72</v>
-      </c>
-      <c r="J77" s="18" t="n">
-        <v>3447.5</v>
-      </c>
-      <c r="K77" s="34" t="n">
-        <v>11146.04</v>
-      </c>
-      <c r="L77" s="18" t="n">
-        <v>1076.04</v>
-      </c>
-      <c r="M77" s="18" t="n">
-        <v>5526.14</v>
-      </c>
-      <c r="N77" s="18" t="n">
-        <v>3148.65</v>
-      </c>
+      <c r="K77" s="9" t="n"/>
       <c r="P77" s="9" t="n"/>
-      <c r="R77" s="5" t="n"/>
+      <c r="R77" s="19" t="n">
+        <v>1.07</v>
+      </c>
       <c r="S77" s="10" t="n"/>
       <c r="T77" s="10" t="n"/>
       <c r="U77" s="11" t="n"/>
@@ -12839,22 +12655,15 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>4.5</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F78" s="9" t="n"/>
-      <c r="J78" s="18" t="n">
-        <v>64.76000000000001</v>
-      </c>
       <c r="K78" s="9" t="n"/>
-      <c r="N78" s="18" t="n">
-        <v>7.5</v>
-      </c>
       <c r="P78" s="9" t="n"/>
-      <c r="R78" s="5" t="n"/>
+      <c r="R78" s="19" t="n">
+        <v>15.1</v>
+      </c>
       <c r="S78" s="10" t="n"/>
       <c r="T78" s="10" t="n"/>
       <c r="U78" s="11" t="n"/>
@@ -12875,48 +12684,48 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E79" s="18" t="n">
-        <v>-1342.74</v>
+        <v>2314.46</v>
       </c>
       <c r="F79" s="9" t="n"/>
       <c r="G79" s="18" t="n">
-        <v>37137.41</v>
+        <v>2688.39</v>
       </c>
       <c r="H79" s="18" t="n">
-        <v>-881.7</v>
+        <v>15647.19</v>
       </c>
       <c r="I79" s="18" t="n">
-        <v>-3912.2</v>
+        <v>2938.3</v>
       </c>
       <c r="J79" s="18" t="n">
-        <v>-3026.29</v>
+        <v>10103.9</v>
       </c>
       <c r="K79" s="34" t="n">
-        <v>29317.22</v>
+        <v>31377.78</v>
       </c>
       <c r="L79" s="18" t="n">
-        <v>-5859.05</v>
+        <v>10071.76</v>
       </c>
       <c r="M79" s="18" t="n">
-        <v>-1286.61</v>
+        <v>7964.27</v>
       </c>
       <c r="N79" s="18" t="n">
-        <v>-7998.58</v>
+        <v>12079.76</v>
       </c>
       <c r="O79" s="18" t="n">
-        <v>-7941.38</v>
+        <v>6901.99</v>
       </c>
       <c r="P79" s="34" t="n">
-        <v>-23085.62</v>
+        <v>37017.78</v>
       </c>
       <c r="Q79" s="18" t="n">
-        <v>-7155.62</v>
+        <v>8954.08</v>
       </c>
       <c r="R79" s="19" t="n">
-        <v>-2812.68</v>
+        <v>10475.1</v>
       </c>
       <c r="S79" s="10" t="n"/>
       <c r="T79" s="10" t="n"/>
@@ -12938,30 +12747,49 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E80" s="18" t="n">
-        <v>21000</v>
+        <v>40.76</v>
       </c>
       <c r="F80" s="9" t="n"/>
       <c r="G80" s="18" t="n">
-        <v>10500</v>
+        <v>110.88</v>
       </c>
       <c r="H80" s="18" t="n">
-        <v>0</v>
+        <v>268.43</v>
       </c>
       <c r="I80" s="18" t="n">
-        <v>0</v>
+        <v>752.84</v>
       </c>
       <c r="J80" s="18" t="n">
-        <v>1000</v>
+        <v>244.72</v>
       </c>
       <c r="K80" s="34" t="n">
-        <v>11500</v>
-      </c>
-      <c r="P80" s="9" t="n"/>
-      <c r="R80" s="5" t="n"/>
+        <v>1376.87</v>
+      </c>
+      <c r="L80" s="18" t="n">
+        <v>249.93</v>
+      </c>
+      <c r="M80" s="18" t="n">
+        <v>154.91</v>
+      </c>
+      <c r="N80" s="18" t="n">
+        <v>284.67</v>
+      </c>
+      <c r="O80" s="18" t="n">
+        <v>200.48</v>
+      </c>
+      <c r="P80" s="34" t="n">
+        <v>889.99</v>
+      </c>
+      <c r="Q80" s="18" t="n">
+        <v>276.05</v>
+      </c>
+      <c r="R80" s="19" t="n">
+        <v>208.22</v>
+      </c>
       <c r="S80" s="10" t="n"/>
       <c r="T80" s="10" t="n"/>
       <c r="U80" s="11" t="n"/>
@@ -12982,48 +12810,48 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E81" s="18" t="n">
-        <v>21477.56</v>
+        <v>-492.18</v>
       </c>
       <c r="F81" s="9" t="n"/>
       <c r="G81" s="18" t="n">
-        <v>10894.23</v>
+        <v>-169.27</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>1960.9</v>
+        <v>-981.99</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>2758.97</v>
+        <v>-695.25</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>2919.23</v>
+        <v>-248.75</v>
       </c>
       <c r="K81" s="34" t="n">
-        <v>18533.33</v>
+        <v>-2095.26</v>
       </c>
       <c r="L81" s="18" t="n">
-        <v>1919.23</v>
+        <v>-664.97</v>
       </c>
       <c r="M81" s="18" t="n">
-        <v>1919.23</v>
+        <v>-830.21</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>2969.23</v>
+        <v>-904.71</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>3819.23</v>
+        <v>-44.36</v>
       </c>
       <c r="P81" s="34" t="n">
-        <v>10626.92</v>
+        <v>-2444.25</v>
       </c>
       <c r="Q81" s="18" t="n">
-        <v>819.23</v>
+        <v>-1927.77</v>
       </c>
       <c r="R81" s="19" t="n">
-        <v>1319.23</v>
+        <v>-2388.87</v>
       </c>
       <c r="S81" s="10" t="n"/>
       <c r="T81" s="10" t="n"/>
@@ -13045,48 +12873,48 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E82" s="18" t="n">
-        <v>777</v>
+        <v>-5324.78</v>
       </c>
       <c r="F82" s="9" t="n"/>
       <c r="G82" s="18" t="n">
-        <v>2100</v>
+        <v>-22956.9</v>
       </c>
       <c r="H82" s="18" t="n">
-        <v>0</v>
+        <v>1960.95</v>
       </c>
       <c r="I82" s="18" t="n">
-        <v>0</v>
+        <v>-10774.79</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>0</v>
+        <v>1360.91</v>
       </c>
       <c r="K82" s="34" t="n">
-        <v>2100</v>
+        <v>-30409.83</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>839</v>
+        <v>-1050</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>1760.5</v>
+        <v>-11463.3</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>143</v>
+        <v>-7046.15</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>0</v>
+        <v>2301.1</v>
       </c>
       <c r="P82" s="34" t="n">
-        <v>2742.5</v>
+        <v>-17258.35</v>
       </c>
       <c r="Q82" s="18" t="n">
-        <v>257.5</v>
+        <v>6919.52</v>
       </c>
       <c r="R82" s="19" t="n">
-        <v>0</v>
+        <v>-6399.3</v>
       </c>
       <c r="S82" s="10" t="n"/>
       <c r="T82" s="10" t="n"/>
@@ -13108,49 +12936,39 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E83" s="18" t="n">
-        <v>-4353.06</v>
+        <v>4928.9</v>
       </c>
       <c r="F83" s="9" t="n"/>
       <c r="G83" s="18" t="n">
-        <v>16869.61</v>
+        <v>1386.73</v>
       </c>
       <c r="H83" s="18" t="n">
-        <v>16733.17</v>
+        <v>1391.09</v>
       </c>
       <c r="I83" s="18" t="n">
-        <v>-11737.86</v>
+        <v>4903.72</v>
       </c>
       <c r="J83" s="18" t="n">
-        <v>8416.85</v>
+        <v>3382.74</v>
       </c>
       <c r="K83" s="34" t="n">
-        <v>30281.77</v>
+        <v>11064.28</v>
       </c>
       <c r="L83" s="18" t="n">
-        <v>3162.71</v>
+        <v>1076.04</v>
       </c>
       <c r="M83" s="18" t="n">
-        <v>-4785.64</v>
+        <v>5491.14</v>
       </c>
       <c r="N83" s="18" t="n">
-        <v>-2964.96</v>
-      </c>
-      <c r="O83" s="18" t="n">
-        <v>1261.15</v>
-      </c>
-      <c r="P83" s="34" t="n">
-        <v>-3326.74</v>
-      </c>
-      <c r="Q83" s="18" t="n">
-        <v>8715.809999999999</v>
-      </c>
-      <c r="R83" s="19" t="n">
-        <v>1267.46</v>
-      </c>
+        <v>3141.15</v>
+      </c>
+      <c r="P83" s="9" t="n"/>
+      <c r="R83" s="5" t="n"/>
       <c r="S83" s="10" t="n"/>
       <c r="T83" s="10" t="n"/>
       <c r="U83" s="11" t="n"/>
@@ -13171,49 +12989,39 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E84" s="18" t="n">
-        <v>-4353.06</v>
+        <v>4933.4</v>
       </c>
       <c r="F84" s="9" t="n"/>
       <c r="G84" s="18" t="n">
-        <v>23353.22</v>
+        <v>1386.73</v>
       </c>
       <c r="H84" s="18" t="n">
-        <v>16733.17</v>
+        <v>1391.09</v>
       </c>
       <c r="I84" s="18" t="n">
-        <v>-11737.86</v>
+        <v>4920.72</v>
       </c>
       <c r="J84" s="18" t="n">
-        <v>8416.85</v>
+        <v>3447.5</v>
       </c>
       <c r="K84" s="34" t="n">
-        <v>36765.38</v>
+        <v>11146.04</v>
       </c>
       <c r="L84" s="18" t="n">
-        <v>39928.09</v>
+        <v>1076.04</v>
       </c>
       <c r="M84" s="18" t="n">
-        <v>-4785.63</v>
+        <v>5526.14</v>
       </c>
       <c r="N84" s="18" t="n">
-        <v>-2964.97</v>
-      </c>
-      <c r="O84" s="18" t="n">
-        <v>1261.15</v>
-      </c>
-      <c r="P84" s="34" t="n">
-        <v>33438.64</v>
-      </c>
-      <c r="Q84" s="18" t="n">
-        <v>42154.45</v>
-      </c>
-      <c r="R84" s="19" t="n">
-        <v>1267.46</v>
-      </c>
+        <v>3148.65</v>
+      </c>
+      <c r="P84" s="9" t="n"/>
+      <c r="R84" s="5" t="n"/>
       <c r="S84" s="10" t="n"/>
       <c r="T84" s="10" t="n"/>
       <c r="U84" s="11" t="n"/>
@@ -13234,33 +13042,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="n">
+        <v>4.5</v>
       </c>
       <c r="F85" s="9" t="n"/>
-      <c r="G85" s="18" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="H85" s="18" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="I85" s="18" t="n">
-        <v>32.41</v>
-      </c>
       <c r="J85" s="18" t="n">
-        <v>65.53</v>
-      </c>
-      <c r="K85" s="34" t="n">
-        <v>110.04</v>
-      </c>
-      <c r="L85" s="18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="M85" s="18" t="n">
-        <v>9.5</v>
-      </c>
+        <v>64.76000000000001</v>
+      </c>
+      <c r="K85" s="9" t="n"/>
       <c r="N85" s="18" t="n">
-        <v>82.62</v>
+        <v>7.5</v>
       </c>
       <c r="P85" s="9" t="n"/>
       <c r="R85" s="5" t="n"/>
@@ -13284,31 +13078,48 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>배당금지급</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="n">
+        <v>-1342.74</v>
       </c>
       <c r="F86" s="9" t="n"/>
-      <c r="K86" s="9" t="n"/>
+      <c r="G86" s="18" t="n">
+        <v>37137.41</v>
+      </c>
+      <c r="H86" s="18" t="n">
+        <v>-881.7</v>
+      </c>
+      <c r="I86" s="18" t="n">
+        <v>-3912.2</v>
+      </c>
+      <c r="J86" s="18" t="n">
+        <v>-3026.29</v>
+      </c>
+      <c r="K86" s="34" t="n">
+        <v>29317.22</v>
+      </c>
       <c r="L86" s="18" t="n">
-        <v>3539.23</v>
+        <v>-5859.05</v>
       </c>
       <c r="M86" s="18" t="n">
-        <v>0</v>
+        <v>-1286.61</v>
       </c>
       <c r="N86" s="18" t="n">
-        <v>0</v>
+        <v>-7998.58</v>
       </c>
       <c r="O86" s="18" t="n">
-        <v>0</v>
+        <v>-7941.38</v>
       </c>
       <c r="P86" s="34" t="n">
-        <v>3539.23</v>
+        <v>-23085.62</v>
       </c>
       <c r="Q86" s="18" t="n">
-        <v>4616.39</v>
+        <v>-7155.62</v>
       </c>
       <c r="R86" s="19" t="n">
-        <v>0</v>
+        <v>-2812.68</v>
       </c>
       <c r="S86" s="10" t="n"/>
       <c r="T86" s="10" t="n"/>
@@ -13330,21 +13141,30 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
-        </is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="n">
+        <v>21000</v>
       </c>
       <c r="F87" s="9" t="n"/>
-      <c r="K87" s="9" t="n"/>
-      <c r="O87" s="18" t="n">
-        <v>2750</v>
+      <c r="G87" s="18" t="n">
+        <v>10500</v>
+      </c>
+      <c r="H87" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K87" s="34" t="n">
+        <v>11500</v>
       </c>
       <c r="P87" s="9" t="n"/>
-      <c r="Q87" s="18" t="n">
-        <v>500</v>
-      </c>
-      <c r="R87" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="R87" s="5" t="n"/>
       <c r="S87" s="10" t="n"/>
       <c r="T87" s="10" t="n"/>
       <c r="U87" s="11" t="n"/>
@@ -13358,6 +13178,389 @@
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
       <c r="AE87" s="11" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="n">
+        <v>21477.56</v>
+      </c>
+      <c r="F88" s="9" t="n"/>
+      <c r="G88" s="18" t="n">
+        <v>10894.23</v>
+      </c>
+      <c r="H88" s="18" t="n">
+        <v>1960.9</v>
+      </c>
+      <c r="I88" s="18" t="n">
+        <v>2758.97</v>
+      </c>
+      <c r="J88" s="18" t="n">
+        <v>2919.23</v>
+      </c>
+      <c r="K88" s="34" t="n">
+        <v>18533.33</v>
+      </c>
+      <c r="L88" s="18" t="n">
+        <v>1919.23</v>
+      </c>
+      <c r="M88" s="18" t="n">
+        <v>1919.23</v>
+      </c>
+      <c r="N88" s="18" t="n">
+        <v>2969.23</v>
+      </c>
+      <c r="O88" s="18" t="n">
+        <v>3819.23</v>
+      </c>
+      <c r="P88" s="34" t="n">
+        <v>10626.92</v>
+      </c>
+      <c r="Q88" s="18" t="n">
+        <v>819.23</v>
+      </c>
+      <c r="R88" s="19" t="n">
+        <v>1319.23</v>
+      </c>
+      <c r="S88" s="10" t="n"/>
+      <c r="T88" s="10" t="n"/>
+      <c r="U88" s="11" t="n"/>
+      <c r="V88" s="10" t="n"/>
+      <c r="W88" s="10" t="n"/>
+      <c r="X88" s="10" t="n"/>
+      <c r="Y88" s="10" t="n"/>
+      <c r="Z88" s="11" t="n"/>
+      <c r="AA88" s="10" t="n"/>
+      <c r="AB88" s="10" t="n"/>
+      <c r="AC88" s="10" t="n"/>
+      <c r="AD88" s="10" t="n"/>
+      <c r="AE88" s="11" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="n">
+        <v>777</v>
+      </c>
+      <c r="F89" s="9" t="n"/>
+      <c r="G89" s="18" t="n">
+        <v>2100</v>
+      </c>
+      <c r="H89" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="34" t="n">
+        <v>2100</v>
+      </c>
+      <c r="L89" s="18" t="n">
+        <v>839</v>
+      </c>
+      <c r="M89" s="18" t="n">
+        <v>1760.5</v>
+      </c>
+      <c r="N89" s="18" t="n">
+        <v>143</v>
+      </c>
+      <c r="O89" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="34" t="n">
+        <v>2742.5</v>
+      </c>
+      <c r="Q89" s="18" t="n">
+        <v>257.5</v>
+      </c>
+      <c r="R89" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="10" t="n"/>
+      <c r="T89" s="10" t="n"/>
+      <c r="U89" s="11" t="n"/>
+      <c r="V89" s="10" t="n"/>
+      <c r="W89" s="10" t="n"/>
+      <c r="X89" s="10" t="n"/>
+      <c r="Y89" s="10" t="n"/>
+      <c r="Z89" s="11" t="n"/>
+      <c r="AA89" s="10" t="n"/>
+      <c r="AB89" s="10" t="n"/>
+      <c r="AC89" s="10" t="n"/>
+      <c r="AD89" s="10" t="n"/>
+      <c r="AE89" s="11" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="n">
+        <v>-4353.06</v>
+      </c>
+      <c r="F90" s="9" t="n"/>
+      <c r="G90" s="18" t="n">
+        <v>16869.61</v>
+      </c>
+      <c r="H90" s="18" t="n">
+        <v>16733.17</v>
+      </c>
+      <c r="I90" s="18" t="n">
+        <v>-11737.86</v>
+      </c>
+      <c r="J90" s="18" t="n">
+        <v>8416.85</v>
+      </c>
+      <c r="K90" s="34" t="n">
+        <v>30281.77</v>
+      </c>
+      <c r="L90" s="18" t="n">
+        <v>3162.71</v>
+      </c>
+      <c r="M90" s="18" t="n">
+        <v>-4785.64</v>
+      </c>
+      <c r="N90" s="18" t="n">
+        <v>-2964.96</v>
+      </c>
+      <c r="O90" s="18" t="n">
+        <v>1261.15</v>
+      </c>
+      <c r="P90" s="34" t="n">
+        <v>-3326.74</v>
+      </c>
+      <c r="Q90" s="18" t="n">
+        <v>8715.809999999999</v>
+      </c>
+      <c r="R90" s="19" t="n">
+        <v>1267.46</v>
+      </c>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
+      <c r="U90" s="11" t="n"/>
+      <c r="V90" s="10" t="n"/>
+      <c r="W90" s="10" t="n"/>
+      <c r="X90" s="10" t="n"/>
+      <c r="Y90" s="10" t="n"/>
+      <c r="Z90" s="11" t="n"/>
+      <c r="AA90" s="10" t="n"/>
+      <c r="AB90" s="10" t="n"/>
+      <c r="AC90" s="10" t="n"/>
+      <c r="AD90" s="10" t="n"/>
+      <c r="AE90" s="11" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="n">
+        <v>-4353.06</v>
+      </c>
+      <c r="F91" s="9" t="n"/>
+      <c r="G91" s="18" t="n">
+        <v>23353.22</v>
+      </c>
+      <c r="H91" s="18" t="n">
+        <v>16733.17</v>
+      </c>
+      <c r="I91" s="18" t="n">
+        <v>-11737.86</v>
+      </c>
+      <c r="J91" s="18" t="n">
+        <v>8416.85</v>
+      </c>
+      <c r="K91" s="34" t="n">
+        <v>36765.38</v>
+      </c>
+      <c r="L91" s="18" t="n">
+        <v>39928.09</v>
+      </c>
+      <c r="M91" s="18" t="n">
+        <v>-4785.63</v>
+      </c>
+      <c r="N91" s="18" t="n">
+        <v>-2964.97</v>
+      </c>
+      <c r="O91" s="18" t="n">
+        <v>1261.15</v>
+      </c>
+      <c r="P91" s="34" t="n">
+        <v>33438.64</v>
+      </c>
+      <c r="Q91" s="18" t="n">
+        <v>42154.45</v>
+      </c>
+      <c r="R91" s="19" t="n">
+        <v>1267.46</v>
+      </c>
+      <c r="S91" s="10" t="n"/>
+      <c r="T91" s="10" t="n"/>
+      <c r="U91" s="11" t="n"/>
+      <c r="V91" s="10" t="n"/>
+      <c r="W91" s="10" t="n"/>
+      <c r="X91" s="10" t="n"/>
+      <c r="Y91" s="10" t="n"/>
+      <c r="Z91" s="11" t="n"/>
+      <c r="AA91" s="10" t="n"/>
+      <c r="AB91" s="10" t="n"/>
+      <c r="AC91" s="10" t="n"/>
+      <c r="AD91" s="10" t="n"/>
+      <c r="AE91" s="11" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>유형자산의감소</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="n"/>
+      <c r="G92" s="18" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="H92" s="18" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="I92" s="18" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="J92" s="18" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="K92" s="34" t="n">
+        <v>110.04</v>
+      </c>
+      <c r="L92" s="18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M92" s="18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="N92" s="18" t="n">
+        <v>82.62</v>
+      </c>
+      <c r="P92" s="9" t="n"/>
+      <c r="R92" s="5" t="n"/>
+      <c r="S92" s="10" t="n"/>
+      <c r="T92" s="10" t="n"/>
+      <c r="U92" s="11" t="n"/>
+      <c r="V92" s="10" t="n"/>
+      <c r="W92" s="10" t="n"/>
+      <c r="X92" s="10" t="n"/>
+      <c r="Y92" s="10" t="n"/>
+      <c r="Z92" s="11" t="n"/>
+      <c r="AA92" s="10" t="n"/>
+      <c r="AB92" s="10" t="n"/>
+      <c r="AC92" s="10" t="n"/>
+      <c r="AD92" s="10" t="n"/>
+      <c r="AE92" s="11" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="n"/>
+      <c r="K93" s="9" t="n"/>
+      <c r="L93" s="18" t="n">
+        <v>3539.23</v>
+      </c>
+      <c r="M93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="34" t="n">
+        <v>3539.23</v>
+      </c>
+      <c r="Q93" s="18" t="n">
+        <v>4616.39</v>
+      </c>
+      <c r="R93" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="10" t="n"/>
+      <c r="T93" s="10" t="n"/>
+      <c r="U93" s="11" t="n"/>
+      <c r="V93" s="10" t="n"/>
+      <c r="W93" s="10" t="n"/>
+      <c r="X93" s="10" t="n"/>
+      <c r="Y93" s="10" t="n"/>
+      <c r="Z93" s="11" t="n"/>
+      <c r="AA93" s="10" t="n"/>
+      <c r="AB93" s="10" t="n"/>
+      <c r="AC93" s="10" t="n"/>
+      <c r="AD93" s="10" t="n"/>
+      <c r="AE93" s="11" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>장기차입금의감소</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="n"/>
+      <c r="K94" s="9" t="n"/>
+      <c r="O94" s="18" t="n">
+        <v>2750</v>
+      </c>
+      <c r="P94" s="9" t="n"/>
+      <c r="Q94" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="R94" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" s="10" t="n"/>
+      <c r="T94" s="10" t="n"/>
+      <c r="U94" s="11" t="n"/>
+      <c r="V94" s="10" t="n"/>
+      <c r="W94" s="10" t="n"/>
+      <c r="X94" s="10" t="n"/>
+      <c r="Y94" s="10" t="n"/>
+      <c r="Z94" s="11" t="n"/>
+      <c r="AA94" s="10" t="n"/>
+      <c r="AB94" s="10" t="n"/>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13562,7 +13765,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/460930_model.xlsx
+++ b/argus/kship/models/460930_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AE$1</definedName>
@@ -687,31 +687,31 @@
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 286144억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 286126억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 297669억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 297630억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AB21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 307777억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 307717억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 320344억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 320265억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 337725억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 337645억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="S22" authorId="0" shapeId="0">
@@ -1614,31 +1614,31 @@
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 286144억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 286126억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 297669억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 297630억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AB5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 307777억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 307717억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 320344억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 320265억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 337725억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 337645억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3879,7 +3879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4582,35 +4582,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -4671,35 +4671,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -4760,35 +4760,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -4849,35 +4849,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5027,35 +5027,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5116,35 +5116,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5205,35 +5205,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5309,7 +5309,7 @@
         <v>12890</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>13090</v>
+        <v>13170</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -5371,7 +5371,7 @@
         <v>16730</v>
       </c>
       <c r="T16" s="20" t="n">
-        <v>13180</v>
+        <v>13220</v>
       </c>
       <c r="U16" s="11" t="n"/>
       <c r="V16" s="10" t="n"/>
@@ -5495,7 +5495,7 @@
         <v>13352.1</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>13060</v>
+        <v>13096.7</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -5625,20 +5625,20 @@
         <v>0.16723906</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.187700326</v>
+        <v>0.187635179</v>
       </c>
       <c r="Z21" s="25" t="n"/>
       <c r="AA21" s="24" t="n">
-        <v>0.182813281</v>
+        <v>0.182664631</v>
       </c>
       <c r="AB21" s="24" t="n">
-        <v>0.169780616</v>
+        <v>0.169548141</v>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.165455014</v>
+        <v>0.165160784</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.180262407</v>
+        <v>0.180052879</v>
       </c>
       <c r="AE21" s="25" t="n"/>
     </row>
@@ -5859,23 +5859,23 @@
         <v>0.118047297</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.118039405</v>
+        <v>0.11804588</v>
       </c>
       <c r="Z23" s="25">
         <f>IFERROR(subQ!Z9/subQ!Z5,"")</f>
         <v/>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.118043575</v>
+        <v>0.118046986</v>
       </c>
       <c r="AB23" s="24" t="n">
-        <v>0.118048219</v>
+        <v>0.118040299</v>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.118045548</v>
+        <v>0.118043792</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.118042904</v>
+        <v>0.11804245</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
@@ -6517,36 +6517,36 @@
         <v/>
       </c>
       <c r="S29" s="30" t="n">
-        <v>-0.003306243</v>
+        <v>-0.004228669</v>
       </c>
       <c r="T29" s="30" t="n">
-        <v>0.001056146</v>
+        <v>6.4268e-05</v>
       </c>
       <c r="U29" s="31" t="n"/>
       <c r="V29" s="30" t="n">
-        <v>0.000884765</v>
+        <v>-5.4491e-05</v>
       </c>
       <c r="W29" s="30" t="n">
-        <v>46.170905208</v>
+        <v>46.169886807</v>
       </c>
       <c r="X29" s="30" t="n">
-        <v>0.000448899</v>
+        <v>-0.000559355</v>
       </c>
       <c r="Y29" s="30" t="n">
-        <v>-0.001685707</v>
+        <v>0.0072057</v>
       </c>
       <c r="Z29" s="31" t="n"/>
       <c r="AA29" s="30" t="n">
-        <v>-0.000937849</v>
+        <v>-0.000116079</v>
       </c>
       <c r="AB29" s="30" t="n">
-        <v>46.172177918</v>
+        <v>46.156688769</v>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.000436936</v>
+        <v>-0.005077449</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.001486528</v>
+        <v>0.002779287</v>
       </c>
       <c r="AE29" s="31" t="n"/>
     </row>
@@ -6611,36 +6611,36 @@
         <v/>
       </c>
       <c r="S30" s="30" t="n">
-        <v>-0.003306243</v>
+        <v>-0.004228669</v>
       </c>
       <c r="T30" s="30" t="n">
-        <v>0.001056146</v>
+        <v>6.4268e-05</v>
       </c>
       <c r="U30" s="31" t="n"/>
       <c r="V30" s="30" t="n">
-        <v>0.000884765</v>
+        <v>-5.4491e-05</v>
       </c>
       <c r="W30" s="30" t="n">
-        <v>46.170905208</v>
+        <v>46.169886807</v>
       </c>
       <c r="X30" s="30" t="n">
-        <v>0.000448899</v>
+        <v>-0.000559355</v>
       </c>
       <c r="Y30" s="30" t="n">
-        <v>-0.001685707</v>
+        <v>0.0072057</v>
       </c>
       <c r="Z30" s="31" t="n"/>
       <c r="AA30" s="30" t="n">
-        <v>-0.000937849</v>
+        <v>-0.000116079</v>
       </c>
       <c r="AB30" s="30" t="n">
-        <v>46.172177918</v>
+        <v>46.156688769</v>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.000436936</v>
+        <v>-0.005077449</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.001486528</v>
+        <v>0.002779287</v>
       </c>
       <c r="AE30" s="31" t="n"/>
     </row>
@@ -6815,20 +6815,20 @@
         <v>0.164174771</v>
       </c>
       <c r="Y32" s="24" t="n">
-        <v>0.15798005</v>
+        <v>0.157962237</v>
       </c>
       <c r="Z32" s="25" t="n"/>
       <c r="AA32" s="24" t="n">
-        <v>0.131674076</v>
+        <v>0.131660719</v>
       </c>
       <c r="AB32" s="24" t="n">
-        <v>0.064592423</v>
+        <v>0.064580586</v>
       </c>
       <c r="AC32" s="24" t="n">
-        <v>0.119227283</v>
+        <v>0.119193544</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.120637927</v>
+        <v>0.120623367</v>
       </c>
       <c r="AE32" s="25" t="n"/>
     </row>
@@ -6909,20 +6909,20 @@
         <v>0.111538407</v>
       </c>
       <c r="Y33" s="24" t="n">
-        <v>0.112385466</v>
+        <v>0.112372793</v>
       </c>
       <c r="Z33" s="25" t="n"/>
       <c r="AA33" s="24" t="n">
-        <v>0.097522073</v>
+        <v>0.097511792</v>
       </c>
       <c r="AB33" s="24" t="n">
-        <v>0.049327866</v>
+        <v>0.04931851</v>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>0.092375874</v>
+        <v>0.09235883</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.095766357</v>
+        <v>0.095743525</v>
       </c>
       <c r="AE33" s="25" t="n"/>
     </row>
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>13090</v>
+        <v>13170</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1906123789831688</v>
+        <v>0.1906229767990182</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.03759220323626099</v>
+        <v>0.03759238649327475</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.02145142721924975</v>
+        <v>0.0214529255882758</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03991623439523782</v>
+        <v>0.03992029209023266</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24168,7 +24168,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27821,7 +27821,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29569,7 +29569,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.95</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="32">
@@ -29579,7 +29579,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/460930_model.xlsx
+++ b/argus/kship/models/460930_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 286126억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 286111억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 297630억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 297590억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AB21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 307717억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 307651억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 320265억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 320174억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 337645억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 337547억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="S22" authorId="0" shapeId="0">
@@ -1614,31 +1614,31 @@
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 286126억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 286111억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 297630억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 297590억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AB5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 307717억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 307651억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 320265억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 320174억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 337645억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 337547억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3879,7 +3879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4582,35 +4582,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -4671,35 +4671,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -4760,35 +4760,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -4849,35 +4849,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5027,35 +5027,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5116,35 +5116,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5205,35 +5205,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5309,7 +5309,7 @@
         <v>12890</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>13170</v>
+        <v>12830</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -5495,7 +5495,7 @@
         <v>13352.1</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>13096.7</v>
+        <v>13037.5</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -5625,20 +5625,20 @@
         <v>0.16723906</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.187635179</v>
+        <v>0.187570033</v>
       </c>
       <c r="Z21" s="25" t="n"/>
       <c r="AA21" s="24" t="n">
-        <v>0.182664631</v>
+        <v>0.182502466</v>
       </c>
       <c r="AB21" s="24" t="n">
-        <v>0.169548141</v>
+        <v>0.16930343</v>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.165160784</v>
+        <v>0.164842036</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.180052879</v>
+        <v>0.1797775</v>
       </c>
       <c r="AE21" s="25" t="n"/>
     </row>
@@ -5859,23 +5859,23 @@
         <v>0.118047297</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.11804588</v>
+        <v>0.118041384</v>
       </c>
       <c r="Z23" s="25">
         <f>IFERROR(subQ!Z9/subQ!Z5,"")</f>
         <v/>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.118046986</v>
+        <v>0.118040318</v>
       </c>
       <c r="AB23" s="24" t="n">
-        <v>0.118040299</v>
+        <v>0.118044074</v>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.118043792</v>
+        <v>0.118044519</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.11804245</v>
+        <v>0.118039281</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
@@ -6517,36 +6517,36 @@
         <v/>
       </c>
       <c r="S29" s="30" t="n">
-        <v>-0.004228669</v>
+        <v>-0.00340929</v>
       </c>
       <c r="T29" s="30" t="n">
-        <v>6.4268e-05</v>
+        <v>0.000995431</v>
       </c>
       <c r="U29" s="31" t="n"/>
       <c r="V29" s="30" t="n">
-        <v>-5.4491e-05</v>
+        <v>0.000871044</v>
       </c>
       <c r="W29" s="30" t="n">
-        <v>46.169886807</v>
+        <v>46.17093667</v>
       </c>
       <c r="X29" s="30" t="n">
-        <v>-0.000559355</v>
+        <v>0.000501352</v>
       </c>
       <c r="Y29" s="30" t="n">
-        <v>0.0072057</v>
+        <v>0.000322763</v>
       </c>
       <c r="Z29" s="31" t="n"/>
       <c r="AA29" s="30" t="n">
-        <v>-0.000116079</v>
+        <v>-0.005103965</v>
       </c>
       <c r="AB29" s="30" t="n">
-        <v>46.156688769</v>
+        <v>46.171791438</v>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.005077449</v>
+        <v>-0.008187292000000001</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.002779287</v>
+        <v>0.001681177</v>
       </c>
       <c r="AE29" s="31" t="n"/>
     </row>
@@ -6611,36 +6611,36 @@
         <v/>
       </c>
       <c r="S30" s="30" t="n">
-        <v>-0.004228669</v>
+        <v>-0.00340929</v>
       </c>
       <c r="T30" s="30" t="n">
-        <v>6.4268e-05</v>
+        <v>0.000995431</v>
       </c>
       <c r="U30" s="31" t="n"/>
       <c r="V30" s="30" t="n">
-        <v>-5.4491e-05</v>
+        <v>0.000871044</v>
       </c>
       <c r="W30" s="30" t="n">
-        <v>46.169886807</v>
+        <v>46.17093667</v>
       </c>
       <c r="X30" s="30" t="n">
-        <v>-0.000559355</v>
+        <v>0.000501352</v>
       </c>
       <c r="Y30" s="30" t="n">
-        <v>0.0072057</v>
+        <v>0.000322763</v>
       </c>
       <c r="Z30" s="31" t="n"/>
       <c r="AA30" s="30" t="n">
-        <v>-0.000116079</v>
+        <v>-0.005103965</v>
       </c>
       <c r="AB30" s="30" t="n">
-        <v>46.156688769</v>
+        <v>46.171791438</v>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.005077449</v>
+        <v>-0.008187292000000001</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.002779287</v>
+        <v>0.001681177</v>
       </c>
       <c r="AE30" s="31" t="n"/>
     </row>
@@ -6819,16 +6819,16 @@
       </c>
       <c r="Z32" s="25" t="n"/>
       <c r="AA32" s="24" t="n">
-        <v>0.131660719</v>
+        <v>0.131629953</v>
       </c>
       <c r="AB32" s="24" t="n">
-        <v>0.064580586</v>
+        <v>0.064555155</v>
       </c>
       <c r="AC32" s="24" t="n">
-        <v>0.119193544</v>
+        <v>0.119174094</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.120623367</v>
+        <v>0.120597396</v>
       </c>
       <c r="AE32" s="25" t="n"/>
     </row>
@@ -6913,16 +6913,16 @@
       </c>
       <c r="Z33" s="25" t="n"/>
       <c r="AA33" s="24" t="n">
-        <v>0.097511792</v>
+        <v>0.097500399</v>
       </c>
       <c r="AB33" s="24" t="n">
-        <v>0.04931851</v>
+        <v>0.049287879</v>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>0.09235883</v>
+        <v>0.092342699</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.095743525</v>
+        <v>0.095721557</v>
       </c>
       <c r="AE33" s="25" t="n"/>
     </row>
@@ -7405,11 +7405,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>13170</v>
+        <v>12830</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 13,030원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 13,110원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1906229767990182</v>
+        <v>0.1906124066217614</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.03759238649327475</v>
+        <v>0.03759416841332323</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.0214529255882758</v>
+        <v>0.02145456888744193</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03992029209023266</v>
+        <v>0.0399248424745088</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24168,7 +24168,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27821,7 +27821,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29569,7 +29569,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.05</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="32">
@@ -29579,7 +29579,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/460930_model.xlsx
+++ b/argus/kship/models/460930_model.xlsx
@@ -3879,7 +3879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/460930_model.xlsx
+++ b/argus/kship/models/460930_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 286111억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 286101억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 297590억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 297580억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AB21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 307651억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 307641억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 320174억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 320164억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 337547억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 337545억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="S22" authorId="0" shapeId="0">
@@ -1614,31 +1614,31 @@
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 286111억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 286101억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 297590억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 297580억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AB5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 307651억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 307641억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 320174억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 320164억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 337547억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 337545억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4582,35 +4582,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -4671,35 +4671,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -4760,35 +4760,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -4849,35 +4849,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5027,35 +5027,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5116,35 +5116,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5205,35 +5205,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5309,7 +5309,7 @@
         <v>12890</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>12830</v>
+        <v>12340</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -5433,7 +5433,7 @@
         <v>10380</v>
       </c>
       <c r="T17" s="20" t="n">
-        <v>12775</v>
+        <v>12300</v>
       </c>
       <c r="U17" s="11" t="n"/>
       <c r="V17" s="10" t="n"/>
@@ -5495,7 +5495,7 @@
         <v>13352.1</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>13037.5</v>
+        <v>12886</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -5625,20 +5625,20 @@
         <v>0.16723906</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.187570033</v>
+        <v>0.187530945</v>
       </c>
       <c r="Z21" s="25" t="n"/>
       <c r="AA21" s="24" t="n">
-        <v>0.182502466</v>
+        <v>0.182461925</v>
       </c>
       <c r="AB21" s="24" t="n">
-        <v>0.16930343</v>
+        <v>0.169266723</v>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.164842036</v>
+        <v>0.164805257</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.1797775</v>
+        <v>0.179805361</v>
       </c>
       <c r="AE21" s="25" t="n"/>
     </row>
@@ -5859,23 +5859,23 @@
         <v>0.118047297</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.118041384</v>
+        <v>0.11804527</v>
       </c>
       <c r="Z23" s="25">
         <f>IFERROR(subQ!Z9/subQ!Z5,"")</f>
         <v/>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.118040318</v>
+        <v>0.118044365</v>
       </c>
       <c r="AB23" s="24" t="n">
-        <v>0.118044074</v>
+        <v>0.11804778</v>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.118044519</v>
+        <v>0.118048247</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.118039281</v>
+        <v>0.118040379</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
@@ -6517,36 +6517,36 @@
         <v/>
       </c>
       <c r="S29" s="30" t="n">
-        <v>-0.00340929</v>
+        <v>-0.003576588</v>
       </c>
       <c r="T29" s="30" t="n">
-        <v>0.000995431</v>
+        <v>0.000818596</v>
       </c>
       <c r="U29" s="31" t="n"/>
       <c r="V29" s="30" t="n">
-        <v>0.000871044</v>
+        <v>0.00070615</v>
       </c>
       <c r="W29" s="30" t="n">
-        <v>46.17093667</v>
+        <v>46.170760727</v>
       </c>
       <c r="X29" s="30" t="n">
-        <v>0.000501352</v>
+        <v>0.000328422</v>
       </c>
       <c r="Y29" s="30" t="n">
-        <v>0.000322763</v>
+        <v>0.000135868</v>
       </c>
       <c r="Z29" s="31" t="n"/>
       <c r="AA29" s="30" t="n">
-        <v>-0.005103965</v>
+        <v>0.004723723</v>
       </c>
       <c r="AB29" s="30" t="n">
-        <v>46.171791438</v>
+        <v>46.161565281</v>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.008187292000000001</v>
+        <v>0.011635375</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.001681177</v>
+        <v>-0.00860297</v>
       </c>
       <c r="AE29" s="31" t="n"/>
     </row>
@@ -6611,36 +6611,36 @@
         <v/>
       </c>
       <c r="S30" s="30" t="n">
-        <v>-0.00340929</v>
+        <v>-0.003576588</v>
       </c>
       <c r="T30" s="30" t="n">
-        <v>0.000995431</v>
+        <v>0.000818596</v>
       </c>
       <c r="U30" s="31" t="n"/>
       <c r="V30" s="30" t="n">
-        <v>0.000871044</v>
+        <v>0.00070615</v>
       </c>
       <c r="W30" s="30" t="n">
-        <v>46.17093667</v>
+        <v>46.170760727</v>
       </c>
       <c r="X30" s="30" t="n">
-        <v>0.000501352</v>
+        <v>0.000328422</v>
       </c>
       <c r="Y30" s="30" t="n">
-        <v>0.000322763</v>
+        <v>0.000135868</v>
       </c>
       <c r="Z30" s="31" t="n"/>
       <c r="AA30" s="30" t="n">
-        <v>-0.005103965</v>
+        <v>0.004723723</v>
       </c>
       <c r="AB30" s="30" t="n">
-        <v>46.171791438</v>
+        <v>46.161565281</v>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.008187292000000001</v>
+        <v>0.011635375</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.001681177</v>
+        <v>-0.00860297</v>
       </c>
       <c r="AE30" s="31" t="n"/>
     </row>
@@ -6815,20 +6815,20 @@
         <v>0.164174771</v>
       </c>
       <c r="Y32" s="24" t="n">
-        <v>0.157962237</v>
+        <v>0.157944425</v>
       </c>
       <c r="Z32" s="25" t="n"/>
       <c r="AA32" s="24" t="n">
-        <v>0.131629953</v>
+        <v>0.131647361</v>
       </c>
       <c r="AB32" s="24" t="n">
-        <v>0.064555155</v>
+        <v>0.064541562</v>
       </c>
       <c r="AC32" s="24" t="n">
-        <v>0.119174094</v>
+        <v>0.119175616</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.120597396</v>
+        <v>0.120587363</v>
       </c>
       <c r="AE32" s="25" t="n"/>
     </row>
@@ -6913,16 +6913,16 @@
       </c>
       <c r="Z33" s="25" t="n"/>
       <c r="AA33" s="24" t="n">
-        <v>0.097500399</v>
+        <v>0.097489006</v>
       </c>
       <c r="AB33" s="24" t="n">
-        <v>0.049287879</v>
+        <v>0.049298772</v>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>0.092342699</v>
+        <v>0.09232291300000001</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.095721557</v>
+        <v>0.09573234799999999</v>
       </c>
       <c r="AE33" s="25" t="n"/>
     </row>
@@ -7405,11 +7405,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>12830</v>
+        <v>12340</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 13,110원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 13,140원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1906124066217614</v>
+        <v>0.1906142487146778</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.03759416841332323</v>
+        <v>0.03759125062886395</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.02145456888744193</v>
+        <v>0.02145501644804577</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.0399248424745088</v>
+        <v>0.03992608138007153</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27821,7 +27821,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29569,7 +29569,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.63</v>
+        <v>15.04</v>
       </c>
     </row>
     <row r="32">
@@ -29579,7 +29579,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/460930_model.xlsx
+++ b/argus/kship/models/460930_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AE$1</definedName>
@@ -681,37 +681,37 @@
     <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 274867억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 275496억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 286101억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 287556억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 297580억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 299289억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AB21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 307641억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 309186억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 320164억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 320615억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 337545억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 336507억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="S22" authorId="0" shapeId="0">
@@ -1608,37 +1608,37 @@
     </comment>
     <comment ref="X5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 274867억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 275496억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 286101억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 287556억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 297580억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 299289억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AB5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 307641억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 309186억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 320164억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 320615억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 337545억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 336507억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -1986,19 +1986,19 @@
     </comment>
     <comment ref="AB11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 963억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 964억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AC11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1011억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1012억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1104억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1106억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2046,19 +2046,19 @@
     </comment>
     <comment ref="AB12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 963억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 964억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AC12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1011억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1012억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1104억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1106억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3879,7 +3879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 2.15% / 부채 3.99% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0215, 0.04] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)"}</t>
+          <t>· 이자율 자산 2.14% / 부채 3.99% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0215, 0.04] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 1.9, "op_wape_pct": 19.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": null, "wape_trend": null, "adopted": "undetermined", "decision": "undetermined", "note": "동결 2024Q2 이전 실적 3분기(&lt;8) 또는 이후 실측 4분기 → OOS 비교 불가(undetermined), 유의성 조건만으로 채택"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 614.67, "rev_act": 605.92, "op_pred": 66.04, "op_act": 67.88}, {"q": "2025Q4", "rev_pred": 673.57, "rev_act": 669.42, "op_pred": 72.37, "op_act": 64.77}, {"q": "2026Q1", "rev_pred": 675.97, "rev_act": 646.1, "op_pred": 72.63, "op_act": 85.3}, {"q": "2026Q2", "rev_pred": 735.12, "rev_act": 727.68, "op_pred": 78.98, "op_act": 121.83}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 7.6, "op_wape_pct": 19.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": null, "wape_trend": null, "adopted": "undetermined", "decision": "undetermined", "note": "동결 2024Q2 이전 실적 3분기(&lt;8) 또는 이후 실측 4분기 → OOS 비교 불가(undetermined), 유의성 조건만으로 채택"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 649.23, "rev_act": 605.92, "op_pred": 69.75, "op_act": 67.88}, {"q": "2025Q4", "rev_pred": 737.31, "rev_act": 669.42, "op_pred": 79.22, "op_act": 64.77}, {"q": "2026Q1", "rev_pred": 699.01, "rev_act": 646.1, "op_pred": 75.1, "op_act": 85.3}, {"q": "2026Q2", "rev_pred": 764.28, "rev_act": 727.68, "op_pred": 82.12, "op_act": 121.83}]}</t>
         </is>
       </c>
     </row>
@@ -5622,23 +5622,23 @@
         <v>0.123141085</v>
       </c>
       <c r="X21" s="24" t="n">
-        <v>0.16723906</v>
+        <v>0.169915</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.187530945</v>
+        <v>0.193563518</v>
       </c>
       <c r="Z21" s="25" t="n"/>
       <c r="AA21" s="24" t="n">
-        <v>0.182461925</v>
+        <v>0.189245801</v>
       </c>
       <c r="AB21" s="24" t="n">
-        <v>0.169266723</v>
+        <v>0.175139791</v>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.164805257</v>
+        <v>0.163780028</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.179805361</v>
+        <v>0.170229024</v>
       </c>
       <c r="AE21" s="25" t="n"/>
     </row>
@@ -5856,26 +5856,26 @@
         <v>0.118048673</v>
       </c>
       <c r="X23" s="24" t="n">
-        <v>0.118047297</v>
+        <v>0.118046382</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.11804527</v>
+        <v>0.118049036</v>
       </c>
       <c r="Z23" s="25">
         <f>IFERROR(subQ!Z9/subQ!Z5,"")</f>
         <v/>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.118044365</v>
+        <v>0.11804143</v>
       </c>
       <c r="AB23" s="24" t="n">
-        <v>0.11804778</v>
+        <v>0.118040878</v>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.118048247</v>
+        <v>0.118039644</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.118040379</v>
+        <v>0.118041045</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
@@ -6517,36 +6517,36 @@
         <v/>
       </c>
       <c r="S29" s="30" t="n">
-        <v>-0.003576588</v>
+        <v>-0.004971177</v>
       </c>
       <c r="T29" s="30" t="n">
-        <v>0.000818596</v>
+        <v>-0.0008165270000000001</v>
       </c>
       <c r="U29" s="31" t="n"/>
       <c r="V29" s="30" t="n">
-        <v>0.00070615</v>
+        <v>-0.001006453</v>
       </c>
       <c r="W29" s="30" t="n">
-        <v>46.170760727</v>
+        <v>46.168784052</v>
       </c>
       <c r="X29" s="30" t="n">
-        <v>0.000328422</v>
+        <v>-0.003640558</v>
       </c>
       <c r="Y29" s="30" t="n">
-        <v>0.000135868</v>
+        <v>0.00372869</v>
       </c>
       <c r="Z29" s="31" t="n"/>
       <c r="AA29" s="30" t="n">
-        <v>0.004723723</v>
+        <v>-0.007485879</v>
       </c>
       <c r="AB29" s="30" t="n">
-        <v>46.161565281</v>
+        <v>46.166907025</v>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.011635375</v>
+        <v>-0.012984898</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.00860297</v>
+        <v>-2.013e-05</v>
       </c>
       <c r="AE29" s="31" t="n"/>
     </row>
@@ -6611,36 +6611,36 @@
         <v/>
       </c>
       <c r="S30" s="30" t="n">
-        <v>-0.003576588</v>
+        <v>-0.004971177</v>
       </c>
       <c r="T30" s="30" t="n">
-        <v>0.000818596</v>
+        <v>-0.0008165270000000001</v>
       </c>
       <c r="U30" s="31" t="n"/>
       <c r="V30" s="30" t="n">
-        <v>0.00070615</v>
+        <v>-0.001006453</v>
       </c>
       <c r="W30" s="30" t="n">
-        <v>46.170760727</v>
+        <v>46.168784052</v>
       </c>
       <c r="X30" s="30" t="n">
-        <v>0.000328422</v>
+        <v>-0.003640558</v>
       </c>
       <c r="Y30" s="30" t="n">
-        <v>0.000135868</v>
+        <v>0.00372869</v>
       </c>
       <c r="Z30" s="31" t="n"/>
       <c r="AA30" s="30" t="n">
-        <v>0.004723723</v>
+        <v>-0.007485879</v>
       </c>
       <c r="AB30" s="30" t="n">
-        <v>46.161565281</v>
+        <v>46.166907025</v>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.011635375</v>
+        <v>-0.012984898</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.00860297</v>
+        <v>-2.013e-05</v>
       </c>
       <c r="AE30" s="31" t="n"/>
     </row>
@@ -6812,23 +6812,23 @@
         <v>0.07353072099999999</v>
       </c>
       <c r="X32" s="24" t="n">
-        <v>0.164174771</v>
+        <v>0.164548037</v>
       </c>
       <c r="Y32" s="24" t="n">
-        <v>0.157944425</v>
+        <v>0.158677303</v>
       </c>
       <c r="Z32" s="25" t="n"/>
       <c r="AA32" s="24" t="n">
-        <v>0.131647361</v>
+        <v>0.132259601</v>
       </c>
       <c r="AB32" s="24" t="n">
-        <v>0.064541562</v>
+        <v>0.065083135</v>
       </c>
       <c r="AC32" s="24" t="n">
-        <v>0.119175616</v>
+        <v>0.119102842</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.120587363</v>
+        <v>0.120012298</v>
       </c>
       <c r="AE32" s="25" t="n"/>
     </row>
@@ -6906,23 +6906,23 @@
         <v>0.048783371</v>
       </c>
       <c r="X33" s="24" t="n">
-        <v>0.111538407</v>
+        <v>0.111791968</v>
       </c>
       <c r="Y33" s="24" t="n">
-        <v>0.112372793</v>
+        <v>0.112904656</v>
       </c>
       <c r="Z33" s="25" t="n"/>
       <c r="AA33" s="24" t="n">
-        <v>0.097489006</v>
+        <v>0.09797805</v>
       </c>
       <c r="AB33" s="24" t="n">
-        <v>0.049298772</v>
+        <v>0.049708633</v>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>0.09232291300000001</v>
+        <v>0.09232881599999999</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.09573234799999999</v>
+        <v>0.095294937</v>
       </c>
       <c r="AE33" s="25" t="n"/>
     </row>
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1906142487146778</v>
+        <v>0.1906296432086139</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.03759125062886395</v>
+        <v>0.0375936361084497</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.02145501644804577</v>
+        <v>0.0214468855494068</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03992608138007153</v>
+        <v>0.03991210525190161</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/460930_model.xlsx
+++ b/argus/kship/models/460930_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AE$1</definedName>
@@ -687,31 +687,31 @@
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 287556억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 287554억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 299289억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 299311억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AB21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 309186억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 309232억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 320615억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 320685억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 336507억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 336602억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="S22" authorId="0" shapeId="0">
@@ -1614,31 +1614,31 @@
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 287556억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 287554억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 299289억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 299311억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AB5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 309186억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 309232억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 320615억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 320685억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 336507억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 336602억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4582,35 +4582,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -4671,35 +4671,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -4760,35 +4760,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -4849,35 +4849,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5027,35 +5027,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5116,35 +5116,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5205,35 +5205,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5309,7 +5309,7 @@
         <v>12890</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>12340</v>
+        <v>12320</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -5495,7 +5495,7 @@
         <v>13352.1</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>12886</v>
+        <v>12882</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -5625,20 +5625,20 @@
         <v>0.169915</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.193563518</v>
+        <v>0.193550489</v>
       </c>
       <c r="Z21" s="25" t="n"/>
       <c r="AA21" s="24" t="n">
-        <v>0.189245801</v>
+        <v>0.189340396</v>
       </c>
       <c r="AB21" s="24" t="n">
-        <v>0.175139791</v>
+        <v>0.175311089</v>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.163780028</v>
+        <v>0.164024659</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.170229024</v>
+        <v>0.170569292</v>
       </c>
       <c r="AE21" s="25" t="n"/>
     </row>
@@ -5859,23 +5859,23 @@
         <v>0.118046382</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.118049036</v>
+        <v>0.118039408</v>
       </c>
       <c r="Z23" s="25">
         <f>IFERROR(subQ!Z9/subQ!Z5,"")</f>
         <v/>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.11804143</v>
+        <v>0.118043404</v>
       </c>
       <c r="AB23" s="24" t="n">
-        <v>0.118040878</v>
+        <v>0.118044494</v>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.118039644</v>
+        <v>0.118046361</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.118041045</v>
+        <v>0.118045323</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
@@ -6517,36 +6517,36 @@
         <v/>
       </c>
       <c r="S29" s="30" t="n">
-        <v>-0.004971177</v>
+        <v>-0.00341714</v>
       </c>
       <c r="T29" s="30" t="n">
-        <v>-0.0008165270000000001</v>
+        <v>0.000880495</v>
       </c>
       <c r="U29" s="31" t="n"/>
       <c r="V29" s="30" t="n">
-        <v>-0.001006453</v>
+        <v>0.000624008</v>
       </c>
       <c r="W29" s="30" t="n">
-        <v>46.168784052</v>
+        <v>46.17057584</v>
       </c>
       <c r="X29" s="30" t="n">
-        <v>-0.003640558</v>
+        <v>-0.001851257</v>
       </c>
       <c r="Y29" s="30" t="n">
-        <v>0.00372869</v>
+        <v>-0.002369472</v>
       </c>
       <c r="Z29" s="31" t="n"/>
       <c r="AA29" s="30" t="n">
-        <v>-0.007485879</v>
+        <v>0.002517458</v>
       </c>
       <c r="AB29" s="30" t="n">
-        <v>46.166907025</v>
+        <v>46.165170064</v>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.012984898</v>
+        <v>-0.006564173</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-2.013e-05</v>
+        <v>0.004833867</v>
       </c>
       <c r="AE29" s="31" t="n"/>
     </row>
@@ -6611,36 +6611,36 @@
         <v/>
       </c>
       <c r="S30" s="30" t="n">
-        <v>-0.004971177</v>
+        <v>-0.00341714</v>
       </c>
       <c r="T30" s="30" t="n">
-        <v>-0.0008165270000000001</v>
+        <v>0.000880495</v>
       </c>
       <c r="U30" s="31" t="n"/>
       <c r="V30" s="30" t="n">
-        <v>-0.001006453</v>
+        <v>0.000624008</v>
       </c>
       <c r="W30" s="30" t="n">
-        <v>46.168784052</v>
+        <v>46.17057584</v>
       </c>
       <c r="X30" s="30" t="n">
-        <v>-0.003640558</v>
+        <v>-0.001851257</v>
       </c>
       <c r="Y30" s="30" t="n">
-        <v>0.00372869</v>
+        <v>-0.002369472</v>
       </c>
       <c r="Z30" s="31" t="n"/>
       <c r="AA30" s="30" t="n">
-        <v>-0.007485879</v>
+        <v>0.002517458</v>
       </c>
       <c r="AB30" s="30" t="n">
-        <v>46.166907025</v>
+        <v>46.165170064</v>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.012984898</v>
+        <v>-0.006564173</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-2.013e-05</v>
+        <v>0.004833867</v>
       </c>
       <c r="AE30" s="31" t="n"/>
     </row>
@@ -6819,16 +6819,16 @@
       </c>
       <c r="Z32" s="25" t="n"/>
       <c r="AA32" s="24" t="n">
-        <v>0.132259601</v>
+        <v>0.13227497</v>
       </c>
       <c r="AB32" s="24" t="n">
-        <v>0.065083135</v>
+        <v>0.065095825</v>
       </c>
       <c r="AC32" s="24" t="n">
-        <v>0.119102842</v>
+        <v>0.119125293</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.120012298</v>
+        <v>0.120040993</v>
       </c>
       <c r="AE32" s="25" t="n"/>
     </row>
@@ -6916,13 +6916,13 @@
         <v>0.09797805</v>
       </c>
       <c r="AB33" s="24" t="n">
-        <v>0.049708633</v>
+        <v>0.049729371</v>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>0.09232881599999999</v>
+        <v>0.09234674700000001</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.095294937</v>
+        <v>0.09531861799999999</v>
       </c>
       <c r="AE33" s="25" t="n"/>
     </row>
@@ -7405,11 +7405,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>12340</v>
+        <v>12320</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 13,140원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,820원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1906296432086139</v>
+        <v>0.1906112526047696</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.0375936361084497</v>
+        <v>0.03759406344817348</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.0214468855494068</v>
+        <v>0.02144594343522998</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03991210525190161</v>
+        <v>0.03990946526860119</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.04</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/460930_model.xlsx
+++ b/argus/kship/models/460930_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 287554억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 287551억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 299311억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 299297억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AB21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 309232억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 309209억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 320685억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 320652억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 336602억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 336563억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="S22" authorId="0" shapeId="0">
@@ -1614,31 +1614,31 @@
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 287554억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 287551억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 299311억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 299297억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AB5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 309232억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 309209억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 320685억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 320652억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 336602억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 336563억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3879,7 +3879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4582,35 +4582,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -4671,35 +4671,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -4760,35 +4760,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -4849,35 +4849,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5027,35 +5027,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5116,35 +5116,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5205,35 +5205,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5625,20 +5625,20 @@
         <v>0.169915</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.193550489</v>
+        <v>0.193537459</v>
       </c>
       <c r="Z21" s="25" t="n"/>
       <c r="AA21" s="24" t="n">
-        <v>0.189340396</v>
+        <v>0.189286342</v>
       </c>
       <c r="AB21" s="24" t="n">
-        <v>0.175311089</v>
+        <v>0.17522544</v>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.164024659</v>
+        <v>0.163914575</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.170569292</v>
+        <v>0.170451072</v>
       </c>
       <c r="AE21" s="25" t="n"/>
     </row>
@@ -5859,23 +5859,23 @@
         <v>0.118046382</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.118039408</v>
+        <v>0.118040697</v>
       </c>
       <c r="Z23" s="25">
         <f>IFERROR(subQ!Z9/subQ!Z5,"")</f>
         <v/>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.118043404</v>
+        <v>0.118048769</v>
       </c>
       <c r="AB23" s="24" t="n">
-        <v>0.118044494</v>
+        <v>0.118042686</v>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.118046361</v>
+        <v>0.118047017</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.118045323</v>
+        <v>0.118039881</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
@@ -6517,36 +6517,36 @@
         <v/>
       </c>
       <c r="S29" s="30" t="n">
-        <v>-0.00341714</v>
+        <v>-0.003098439</v>
       </c>
       <c r="T29" s="30" t="n">
-        <v>0.000880495</v>
+        <v>0.00124291</v>
       </c>
       <c r="U29" s="31" t="n"/>
       <c r="V29" s="30" t="n">
-        <v>0.000624008</v>
+        <v>0.000984256</v>
       </c>
       <c r="W29" s="30" t="n">
-        <v>46.17057584</v>
+        <v>46.170984705</v>
       </c>
       <c r="X29" s="30" t="n">
-        <v>-0.001851257</v>
+        <v>-0.00143723</v>
       </c>
       <c r="Y29" s="30" t="n">
-        <v>-0.002369472</v>
+        <v>-0.001895081</v>
       </c>
       <c r="Z29" s="31" t="n"/>
       <c r="AA29" s="30" t="n">
-        <v>0.002517458</v>
+        <v>0.002987549</v>
       </c>
       <c r="AB29" s="30" t="n">
-        <v>46.165170064</v>
+        <v>46.167598952</v>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.006564173</v>
+        <v>0.005824078</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.004833867</v>
+        <v>-0.010885789</v>
       </c>
       <c r="AE29" s="31" t="n"/>
     </row>
@@ -6611,36 +6611,36 @@
         <v/>
       </c>
       <c r="S30" s="30" t="n">
-        <v>-0.00341714</v>
+        <v>-0.003098439</v>
       </c>
       <c r="T30" s="30" t="n">
-        <v>0.000880495</v>
+        <v>0.00124291</v>
       </c>
       <c r="U30" s="31" t="n"/>
       <c r="V30" s="30" t="n">
-        <v>0.000624008</v>
+        <v>0.000984256</v>
       </c>
       <c r="W30" s="30" t="n">
-        <v>46.17057584</v>
+        <v>46.170984705</v>
       </c>
       <c r="X30" s="30" t="n">
-        <v>-0.001851257</v>
+        <v>-0.00143723</v>
       </c>
       <c r="Y30" s="30" t="n">
-        <v>-0.002369472</v>
+        <v>-0.001895081</v>
       </c>
       <c r="Z30" s="31" t="n"/>
       <c r="AA30" s="30" t="n">
-        <v>0.002517458</v>
+        <v>0.002987549</v>
       </c>
       <c r="AB30" s="30" t="n">
-        <v>46.165170064</v>
+        <v>46.167598952</v>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.006564173</v>
+        <v>0.005824078</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.004833867</v>
+        <v>-0.010885789</v>
       </c>
       <c r="AE30" s="31" t="n"/>
     </row>
@@ -6819,16 +6819,16 @@
       </c>
       <c r="Z32" s="25" t="n"/>
       <c r="AA32" s="24" t="n">
-        <v>0.13227497</v>
+        <v>0.132259601</v>
       </c>
       <c r="AB32" s="24" t="n">
-        <v>0.065095825</v>
+        <v>0.065096709</v>
       </c>
       <c r="AC32" s="24" t="n">
-        <v>0.119125293</v>
+        <v>0.119114068</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.120040993</v>
+        <v>0.120020952</v>
       </c>
       <c r="AE32" s="25" t="n"/>
     </row>
@@ -6916,13 +6916,13 @@
         <v>0.09797805</v>
       </c>
       <c r="AB33" s="24" t="n">
-        <v>0.049729371</v>
+        <v>0.049719002</v>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>0.09234674700000001</v>
+        <v>0.092327904</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.09531861799999999</v>
+        <v>0.09532120400000001</v>
       </c>
       <c r="AE33" s="25" t="n"/>
     </row>
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1906112526047696</v>
+        <v>0.1906071218392135</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.03759406344817348</v>
+        <v>0.03759318263274067</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.02144594343522998</v>
+        <v>0.02144658781719191</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03990946526860119</v>
+        <v>0.03991128074800268</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/460930_model.xlsx
+++ b/argus/kship/models/460930_model.xlsx
@@ -3879,7 +3879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/460930_model.xlsx
+++ b/argus/kship/models/460930_model.xlsx
@@ -3879,7 +3879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
         <v>12890</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>12320</v>
+        <v>11790</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -5433,7 +5433,7 @@
         <v>10380</v>
       </c>
       <c r="T17" s="20" t="n">
-        <v>12300</v>
+        <v>11770</v>
       </c>
       <c r="U17" s="11" t="n"/>
       <c r="V17" s="10" t="n"/>
@@ -5495,7 +5495,7 @@
         <v>13352.1</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>12882</v>
+        <v>12700</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>12320</v>
+        <v>11790</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24168,7 +24168,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27821,7 +27821,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29569,7 +29569,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.01</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="32">
@@ -29579,7 +29579,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/460930_model.xlsx
+++ b/argus/kship/models/460930_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 287551억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 287543억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 299297억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 299246억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AB21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 309209억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 309112억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 320652억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 320506억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 336563억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 336377억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="S22" authorId="0" shapeId="0">
@@ -1614,31 +1614,31 @@
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 287551억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 287543억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 299297억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 299246억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AB5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 309209억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 309112억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 320652억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 320506억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 336563억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 336377억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3879,7 +3879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4582,35 +4582,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -4671,35 +4671,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -4760,35 +4760,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -4849,35 +4849,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5027,35 +5027,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5116,35 +5116,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5205,35 +5205,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5309,7 +5309,7 @@
         <v>12890</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>11790</v>
+        <v>11670</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -5433,7 +5433,7 @@
         <v>10380</v>
       </c>
       <c r="T17" s="20" t="n">
-        <v>11770</v>
+        <v>11260</v>
       </c>
       <c r="U17" s="11" t="n"/>
       <c r="V17" s="10" t="n"/>
@@ -5495,7 +5495,7 @@
         <v>13352.1</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>12700</v>
+        <v>12544.3</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -5625,20 +5625,20 @@
         <v>0.169915</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.193537459</v>
+        <v>0.193511401</v>
       </c>
       <c r="Z21" s="25" t="n"/>
       <c r="AA21" s="24" t="n">
-        <v>0.189286342</v>
+        <v>0.189083636</v>
       </c>
       <c r="AB21" s="24" t="n">
-        <v>0.17522544</v>
+        <v>0.174858373</v>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.163914575</v>
+        <v>0.163376388</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.170451072</v>
+        <v>0.169832536</v>
       </c>
       <c r="AE21" s="25" t="n"/>
     </row>
@@ -5859,23 +5859,23 @@
         <v>0.118046382</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.118040697</v>
+        <v>0.118043274</v>
       </c>
       <c r="Z23" s="25">
         <f>IFERROR(subQ!Z9/subQ!Z5,"")</f>
         <v/>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.118048769</v>
+        <v>0.118046164</v>
       </c>
       <c r="AB23" s="24" t="n">
-        <v>0.118042686</v>
+        <v>0.118048323</v>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.118047017</v>
+        <v>0.118049057</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.118039881</v>
+        <v>0.118039549</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
@@ -6517,36 +6517,36 @@
         <v/>
       </c>
       <c r="S29" s="30" t="n">
-        <v>-0.003098439</v>
+        <v>-0.003815323</v>
       </c>
       <c r="T29" s="30" t="n">
-        <v>0.00124291</v>
+        <v>0.0004886270000000001</v>
       </c>
       <c r="U29" s="31" t="n"/>
       <c r="V29" s="30" t="n">
-        <v>0.000984256</v>
+        <v>0.000284271</v>
       </c>
       <c r="W29" s="30" t="n">
-        <v>46.170984705</v>
+        <v>46.1702411</v>
       </c>
       <c r="X29" s="30" t="n">
-        <v>-0.00143723</v>
+        <v>-0.002168172</v>
       </c>
       <c r="Y29" s="30" t="n">
-        <v>-0.001895081</v>
+        <v>0.007313775</v>
       </c>
       <c r="Z29" s="31" t="n"/>
       <c r="AA29" s="30" t="n">
-        <v>0.002987549</v>
+        <v>-0.003966136</v>
       </c>
       <c r="AB29" s="30" t="n">
-        <v>46.167598952</v>
+        <v>46.162466735</v>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.005824078</v>
+        <v>0.004444141</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.010885789</v>
+        <v>0.001298879</v>
       </c>
       <c r="AE29" s="31" t="n"/>
     </row>
@@ -6611,36 +6611,36 @@
         <v/>
       </c>
       <c r="S30" s="30" t="n">
-        <v>-0.003098439</v>
+        <v>-0.003815323</v>
       </c>
       <c r="T30" s="30" t="n">
-        <v>0.00124291</v>
+        <v>0.0004886270000000001</v>
       </c>
       <c r="U30" s="31" t="n"/>
       <c r="V30" s="30" t="n">
-        <v>0.000984256</v>
+        <v>0.000284271</v>
       </c>
       <c r="W30" s="30" t="n">
-        <v>46.170984705</v>
+        <v>46.1702411</v>
       </c>
       <c r="X30" s="30" t="n">
-        <v>-0.00143723</v>
+        <v>-0.002168172</v>
       </c>
       <c r="Y30" s="30" t="n">
-        <v>-0.001895081</v>
+        <v>0.007313775</v>
       </c>
       <c r="Z30" s="31" t="n"/>
       <c r="AA30" s="30" t="n">
-        <v>0.002987549</v>
+        <v>-0.003966136</v>
       </c>
       <c r="AB30" s="30" t="n">
-        <v>46.167598952</v>
+        <v>46.162466735</v>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.005824078</v>
+        <v>0.004444141</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.010885789</v>
+        <v>0.001298879</v>
       </c>
       <c r="AE30" s="31" t="n"/>
     </row>
@@ -6819,16 +6819,16 @@
       </c>
       <c r="Z32" s="25" t="n"/>
       <c r="AA32" s="24" t="n">
-        <v>0.132259601</v>
+        <v>0.132244233</v>
       </c>
       <c r="AB32" s="24" t="n">
-        <v>0.065096709</v>
+        <v>0.065043299</v>
       </c>
       <c r="AC32" s="24" t="n">
-        <v>0.119114068</v>
+        <v>0.11907068</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.120020952</v>
+        <v>0.119976312</v>
       </c>
       <c r="AE32" s="25" t="n"/>
     </row>
@@ -6909,20 +6909,20 @@
         <v>0.111791968</v>
       </c>
       <c r="Y33" s="24" t="n">
-        <v>0.112904656</v>
+        <v>0.112891986</v>
       </c>
       <c r="Z33" s="25" t="n"/>
       <c r="AA33" s="24" t="n">
-        <v>0.09797805</v>
+        <v>0.09796778</v>
       </c>
       <c r="AB33" s="24" t="n">
-        <v>0.049719002</v>
+        <v>0.049699295</v>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>0.092327904</v>
+        <v>0.09229203900000001</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.09532120400000001</v>
+        <v>0.095264795</v>
       </c>
       <c r="AE33" s="25" t="n"/>
     </row>
@@ -7405,11 +7405,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>11790</v>
+        <v>11670</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,820원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,350원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1906071218392135</v>
+        <v>0.1906149585556724</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.03759318263274067</v>
+        <v>0.03759508399642228</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.02144658781719191</v>
+        <v>0.02144872604258016</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03991128074800268</v>
+        <v>0.03991714193834061</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24168,7 +24168,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27821,7 +27821,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29569,7 +29569,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.37</v>
+        <v>14.22</v>
       </c>
     </row>
     <row r="32">
@@ -29579,7 +29579,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/460930_model.xlsx
+++ b/argus/kship/models/460930_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 287543억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 287541억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 299246억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 299287억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AB21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 309112억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 309196억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 320506억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 320631억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 336377억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 336542억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="S22" authorId="0" shapeId="0">
@@ -1614,31 +1614,31 @@
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 287543억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 287541억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 299246억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 299287억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AB5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 309112억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 309196억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 320506억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 320631억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 336377억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 336542억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3879,7 +3879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4582,35 +4582,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -4671,35 +4671,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -4760,35 +4760,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -4849,35 +4849,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5027,35 +5027,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5116,35 +5116,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5205,35 +5205,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5309,7 +5309,7 @@
         <v>12890</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>11670</v>
+        <v>11840</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -5495,7 +5495,7 @@
         <v>13352.1</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>12544.3</v>
+        <v>12462.5</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -5625,20 +5625,20 @@
         <v>0.169915</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.193511401</v>
+        <v>0.193498371</v>
       </c>
       <c r="Z21" s="25" t="n"/>
       <c r="AA21" s="24" t="n">
-        <v>0.189083636</v>
+        <v>0.189245801</v>
       </c>
       <c r="AB21" s="24" t="n">
-        <v>0.174858373</v>
+        <v>0.175176498</v>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.163376388</v>
+        <v>0.163828954</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.169832536</v>
+        <v>0.170423904</v>
       </c>
       <c r="AE21" s="25" t="n"/>
     </row>
@@ -5859,23 +5859,23 @@
         <v>0.118046382</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.118043274</v>
+        <v>0.118044563</v>
       </c>
       <c r="Z23" s="25">
         <f>IFERROR(subQ!Z9/subQ!Z5,"")</f>
         <v/>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.118046164</v>
+        <v>0.11804143</v>
       </c>
       <c r="AB23" s="24" t="n">
-        <v>0.118048323</v>
+        <v>0.118047602</v>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.118049057</v>
+        <v>0.118045192</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.118039549</v>
+        <v>0.118046487</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
@@ -6517,36 +6517,36 @@
         <v/>
       </c>
       <c r="S29" s="30" t="n">
-        <v>-0.003815323</v>
+        <v>-0.003717781</v>
       </c>
       <c r="T29" s="30" t="n">
-        <v>0.0004886270000000001</v>
+        <v>0.000567396</v>
       </c>
       <c r="U29" s="31" t="n"/>
       <c r="V29" s="30" t="n">
-        <v>0.000284271</v>
+        <v>0.000336486</v>
       </c>
       <c r="W29" s="30" t="n">
-        <v>46.1702411</v>
+        <v>46.170273496</v>
       </c>
       <c r="X29" s="30" t="n">
-        <v>-0.002168172</v>
+        <v>-0.002146943</v>
       </c>
       <c r="Y29" s="30" t="n">
-        <v>0.007313775</v>
+        <v>0.007313915</v>
       </c>
       <c r="Z29" s="31" t="n"/>
       <c r="AA29" s="30" t="n">
-        <v>-0.003966136</v>
+        <v>-0.005904934</v>
       </c>
       <c r="AB29" s="30" t="n">
-        <v>46.162466735</v>
+        <v>46.166734937</v>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.004444141</v>
+        <v>-0.003123372</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.001298879</v>
+        <v>-0.001839294</v>
       </c>
       <c r="AE29" s="31" t="n"/>
     </row>
@@ -6611,36 +6611,36 @@
         <v/>
       </c>
       <c r="S30" s="30" t="n">
-        <v>-0.003815323</v>
+        <v>-0.003717781</v>
       </c>
       <c r="T30" s="30" t="n">
-        <v>0.0004886270000000001</v>
+        <v>0.000567396</v>
       </c>
       <c r="U30" s="31" t="n"/>
       <c r="V30" s="30" t="n">
-        <v>0.000284271</v>
+        <v>0.000336486</v>
       </c>
       <c r="W30" s="30" t="n">
-        <v>46.1702411</v>
+        <v>46.170273496</v>
       </c>
       <c r="X30" s="30" t="n">
-        <v>-0.002168172</v>
+        <v>-0.002146943</v>
       </c>
       <c r="Y30" s="30" t="n">
-        <v>0.007313775</v>
+        <v>0.007313915</v>
       </c>
       <c r="Z30" s="31" t="n"/>
       <c r="AA30" s="30" t="n">
-        <v>-0.003966136</v>
+        <v>-0.005904934</v>
       </c>
       <c r="AB30" s="30" t="n">
-        <v>46.162466735</v>
+        <v>46.166734937</v>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.004444141</v>
+        <v>-0.003123372</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.001298879</v>
+        <v>-0.001839294</v>
       </c>
       <c r="AE30" s="31" t="n"/>
     </row>
@@ -6819,16 +6819,16 @@
       </c>
       <c r="Z32" s="25" t="n"/>
       <c r="AA32" s="24" t="n">
-        <v>0.132244233</v>
+        <v>0.132259601</v>
       </c>
       <c r="AB32" s="24" t="n">
-        <v>0.065043299</v>
+        <v>0.065083135</v>
       </c>
       <c r="AC32" s="24" t="n">
-        <v>0.11907068</v>
+        <v>0.119115586</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.119976312</v>
+        <v>0.120010932</v>
       </c>
       <c r="AE32" s="25" t="n"/>
     </row>
@@ -6913,16 +6913,16 @@
       </c>
       <c r="Z33" s="25" t="n"/>
       <c r="AA33" s="24" t="n">
-        <v>0.09796778</v>
+        <v>0.09797916499999999</v>
       </c>
       <c r="AB33" s="24" t="n">
-        <v>0.049699295</v>
+        <v>0.049719518</v>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>0.09229203900000001</v>
+        <v>0.09232881599999999</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.095264795</v>
+        <v>0.095313023</v>
       </c>
       <c r="AE33" s="25" t="n"/>
     </row>
@@ -7405,11 +7405,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>11670</v>
+        <v>11840</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,350원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 11,850원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1906149585556724</v>
+        <v>0.1906144777084197</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.03759508399642228</v>
+        <v>0.03759302562960489</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.02144872604258016</v>
+        <v>0.02144703980411972</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03991714193834061</v>
+        <v>0.03991244153237655</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24168,7 +24168,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27821,7 +27821,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29569,7 +29569,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.22</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="32">
@@ -29579,7 +29579,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/460930_model.xlsx
+++ b/argus/kship/models/460930_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 287541억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 287947억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 299287억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 299966억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AB21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 309196억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 309896억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 320631억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 321155억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 336542억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 336338억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="S22" authorId="0" shapeId="0">
@@ -1614,31 +1614,31 @@
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 287541억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 287947억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 299287억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 299966억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AB5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 309196억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 309896억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 320631억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 321155억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 336542억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 336338억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -1986,19 +1986,19 @@
     </comment>
     <comment ref="AB11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 964억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 965억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AC11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1012억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1013억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1106억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1107억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2046,19 +2046,19 @@
     </comment>
     <comment ref="AB12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 964억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 965억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AC12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1012억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1013억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1106억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1107억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3879,7 +3879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4582,35 +4582,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -4671,35 +4671,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -4760,35 +4760,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -4849,35 +4849,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5027,35 +5027,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5116,35 +5116,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5205,35 +5205,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5309,7 +5309,7 @@
         <v>12890</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>11840</v>
+        <v>11470</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -5433,7 +5433,7 @@
         <v>10380</v>
       </c>
       <c r="T17" s="20" t="n">
-        <v>11260</v>
+        <v>10830</v>
       </c>
       <c r="U17" s="11" t="n"/>
       <c r="V17" s="10" t="n"/>
@@ -5495,7 +5495,7 @@
         <v>13352.1</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>12462.5</v>
+        <v>12113.6</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -5625,20 +5625,20 @@
         <v>0.169915</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.193498371</v>
+        <v>0.195192182</v>
       </c>
       <c r="Z21" s="25" t="n"/>
       <c r="AA21" s="24" t="n">
-        <v>0.189245801</v>
+        <v>0.19194854</v>
       </c>
       <c r="AB21" s="24" t="n">
-        <v>0.175176498</v>
+        <v>0.177831614</v>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.163828954</v>
+        <v>0.165737071</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.170423904</v>
+        <v>0.168045699</v>
       </c>
       <c r="AE21" s="25" t="n"/>
     </row>
@@ -5859,23 +5859,23 @@
         <v>0.118046382</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.118044563</v>
+        <v>0.118040793</v>
       </c>
       <c r="Z23" s="25">
         <f>IFERROR(subQ!Z9/subQ!Z5,"")</f>
         <v/>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.11804143</v>
+        <v>0.118045871</v>
       </c>
       <c r="AB23" s="24" t="n">
-        <v>0.118047602</v>
+        <v>0.1180412</v>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.118045192</v>
+        <v>0.118040837</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.118046487</v>
+        <v>0.118044537</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
@@ -6517,36 +6517,36 @@
         <v/>
       </c>
       <c r="S29" s="30" t="n">
-        <v>-0.003717781</v>
+        <v>-0.00361218</v>
       </c>
       <c r="T29" s="30" t="n">
-        <v>0.000567396</v>
+        <v>0.000316228</v>
       </c>
       <c r="U29" s="31" t="n"/>
       <c r="V29" s="30" t="n">
-        <v>0.000336486</v>
+        <v>-0.000225188</v>
       </c>
       <c r="W29" s="30" t="n">
-        <v>46.170273496</v>
+        <v>46.169327709</v>
       </c>
       <c r="X29" s="30" t="n">
-        <v>-0.002146943</v>
+        <v>-0.003241731</v>
       </c>
       <c r="Y29" s="30" t="n">
-        <v>0.007313915</v>
+        <v>-0.002810809</v>
       </c>
       <c r="Z29" s="31" t="n"/>
       <c r="AA29" s="30" t="n">
-        <v>-0.005904934</v>
+        <v>-0.002994442</v>
       </c>
       <c r="AB29" s="30" t="n">
-        <v>46.166734937</v>
+        <v>46.158111095</v>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.003123372</v>
+        <v>0.002297326</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.001839294</v>
+        <v>-0.006767971</v>
       </c>
       <c r="AE29" s="31" t="n"/>
     </row>
@@ -6611,36 +6611,36 @@
         <v/>
       </c>
       <c r="S30" s="30" t="n">
-        <v>-0.003717781</v>
+        <v>-0.00361218</v>
       </c>
       <c r="T30" s="30" t="n">
-        <v>0.000567396</v>
+        <v>0.000316228</v>
       </c>
       <c r="U30" s="31" t="n"/>
       <c r="V30" s="30" t="n">
-        <v>0.000336486</v>
+        <v>-0.000225188</v>
       </c>
       <c r="W30" s="30" t="n">
-        <v>46.170273496</v>
+        <v>46.169327709</v>
       </c>
       <c r="X30" s="30" t="n">
-        <v>-0.002146943</v>
+        <v>-0.003241731</v>
       </c>
       <c r="Y30" s="30" t="n">
-        <v>0.007313915</v>
+        <v>-0.002810809</v>
       </c>
       <c r="Z30" s="31" t="n"/>
       <c r="AA30" s="30" t="n">
-        <v>-0.005904934</v>
+        <v>-0.002994442</v>
       </c>
       <c r="AB30" s="30" t="n">
-        <v>46.166734937</v>
+        <v>46.158111095</v>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.003123372</v>
+        <v>0.002297326</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.001839294</v>
+        <v>-0.006767971</v>
       </c>
       <c r="AE30" s="31" t="n"/>
     </row>
@@ -6815,20 +6815,20 @@
         <v>0.164548037</v>
       </c>
       <c r="Y32" s="24" t="n">
-        <v>0.158677303</v>
+        <v>0.158890986</v>
       </c>
       <c r="Z32" s="25" t="n"/>
       <c r="AA32" s="24" t="n">
-        <v>0.132259601</v>
+        <v>0.132527158</v>
       </c>
       <c r="AB32" s="24" t="n">
-        <v>0.065083135</v>
+        <v>0.065340678</v>
       </c>
       <c r="AC32" s="24" t="n">
-        <v>0.119115586</v>
+        <v>0.119227732</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.120010932</v>
+        <v>0.119862546</v>
       </c>
       <c r="AE32" s="25" t="n"/>
     </row>
@@ -6909,20 +6909,20 @@
         <v>0.111791968</v>
       </c>
       <c r="Y33" s="24" t="n">
-        <v>0.112891986</v>
+        <v>0.113056699</v>
       </c>
       <c r="Z33" s="25" t="n"/>
       <c r="AA33" s="24" t="n">
-        <v>0.09797916499999999</v>
+        <v>0.098180949</v>
       </c>
       <c r="AB33" s="24" t="n">
-        <v>0.049719518</v>
+        <v>0.049920703</v>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>0.09232881599999999</v>
+        <v>0.09241872299999999</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.095313023</v>
+        <v>0.095201085</v>
       </c>
       <c r="AE33" s="25" t="n"/>
     </row>
@@ -7405,11 +7405,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>11840</v>
+        <v>11470</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 11,850원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 11,000원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1906144777084197</v>
+        <v>0.1906212641240215</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.03759302562960489</v>
+        <v>0.03759308734128065</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.02144703980411972</v>
+        <v>0.02142494935652891</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03991244153237655</v>
+        <v>0.03985281764317002</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24168,7 +24168,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27821,7 +27821,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29569,7 +29569,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.43</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="32">
@@ -29579,7 +29579,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/460930_model.xlsx
+++ b/argus/kship/models/460930_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 287947억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 288262억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 299966억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 300545억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AB21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 309896억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 310545억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 321155억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 321725억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 336338억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 336402억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="S22" authorId="0" shapeId="0">
@@ -1614,31 +1614,31 @@
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 287947억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 288262억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 299966억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 300545억 × 비례계수 0.0122 × 계절비중 Q1 0.241(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AB5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 309896억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 310545억 × 비례계수 0.0122 × 계절비중 Q2 0.255(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 321155억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 321725억 × 비례계수 0.0122 × 계절비중 Q3 0.243(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 336338억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 336402억 × 비례계수 0.0122 × 계절비중 Q4 0.261(계절비중 — 최근 2개 연도(2026, 2025) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -1980,7 +1980,7 @@
     </comment>
     <comment ref="AA11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 878억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 879억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2040,7 +2040,7 @@
     </comment>
     <comment ref="AA12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 878억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 879억 × 2.15%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 227억 × 4.00%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3879,7 +3879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4582,35 +4582,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -4671,35 +4671,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -4760,35 +4760,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -4849,35 +4849,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -4938,35 +4938,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5027,35 +5027,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5116,35 +5116,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5205,35 +5205,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5309,7 +5309,7 @@
         <v>12890</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>11470</v>
+        <v>10010</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -5433,7 +5433,7 @@
         <v>10380</v>
       </c>
       <c r="T17" s="20" t="n">
-        <v>10830</v>
+        <v>10010</v>
       </c>
       <c r="U17" s="11" t="n"/>
       <c r="V17" s="10" t="n"/>
@@ -5495,7 +5495,7 @@
         <v>13352.1</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>12113.6</v>
+        <v>11632.5</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -5625,20 +5625,20 @@
         <v>0.169915</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.195192182</v>
+        <v>0.196495114</v>
       </c>
       <c r="Z21" s="25" t="n"/>
       <c r="AA21" s="24" t="n">
-        <v>0.19194854</v>
+        <v>0.194245868</v>
       </c>
       <c r="AB21" s="24" t="n">
-        <v>0.177831614</v>
+        <v>0.180303197</v>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.165737071</v>
+        <v>0.167804198</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.168045699</v>
+        <v>0.167002428</v>
       </c>
       <c r="AE21" s="25" t="n"/>
     </row>
@@ -5859,23 +5859,23 @@
         <v>0.118046382</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.118040793</v>
+        <v>0.118042927</v>
       </c>
       <c r="Z23" s="25">
         <f>IFERROR(subQ!Z9/subQ!Z5,"")</f>
         <v/>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.118045871</v>
+        <v>0.118045104</v>
       </c>
       <c r="AB23" s="24" t="n">
-        <v>0.1180412</v>
+        <v>0.118042813</v>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.118040837</v>
+        <v>0.118041372</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.118044537</v>
+        <v>0.118040068</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
@@ -6517,36 +6517,36 @@
         <v/>
       </c>
       <c r="S29" s="30" t="n">
-        <v>-0.00361218</v>
+        <v>-0.004029815</v>
       </c>
       <c r="T29" s="30" t="n">
-        <v>0.000316228</v>
+        <v>9.5202e-05</v>
       </c>
       <c r="U29" s="31" t="n"/>
       <c r="V29" s="30" t="n">
-        <v>-0.000225188</v>
+        <v>-0.000258838</v>
       </c>
       <c r="W29" s="30" t="n">
-        <v>46.169327709</v>
+        <v>46.169505106</v>
       </c>
       <c r="X29" s="30" t="n">
-        <v>-0.003241731</v>
+        <v>-0.002976927</v>
       </c>
       <c r="Y29" s="30" t="n">
-        <v>-0.002810809</v>
+        <v>0.004818353</v>
       </c>
       <c r="Z29" s="31" t="n"/>
       <c r="AA29" s="30" t="n">
-        <v>-0.002994442</v>
+        <v>1.317e-06</v>
       </c>
       <c r="AB29" s="30" t="n">
-        <v>46.158111095</v>
+        <v>46.154426415</v>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.002297326</v>
+        <v>-0.002769851</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.006767971</v>
+        <v>-0.006504938</v>
       </c>
       <c r="AE29" s="31" t="n"/>
     </row>
@@ -6611,36 +6611,36 @@
         <v/>
       </c>
       <c r="S30" s="30" t="n">
-        <v>-0.00361218</v>
+        <v>-0.004029815</v>
       </c>
       <c r="T30" s="30" t="n">
-        <v>0.000316228</v>
+        <v>9.5202e-05</v>
       </c>
       <c r="U30" s="31" t="n"/>
       <c r="V30" s="30" t="n">
-        <v>-0.000225188</v>
+        <v>-0.000258838</v>
       </c>
       <c r="W30" s="30" t="n">
-        <v>46.169327709</v>
+        <v>46.169505106</v>
       </c>
       <c r="X30" s="30" t="n">
-        <v>-0.003241731</v>
+        <v>-0.002976927</v>
       </c>
       <c r="Y30" s="30" t="n">
-        <v>-0.002810809</v>
+        <v>0.004818353</v>
       </c>
       <c r="Z30" s="31" t="n"/>
       <c r="AA30" s="30" t="n">
-        <v>-0.002994442</v>
+        <v>1.317e-06</v>
       </c>
       <c r="AB30" s="30" t="n">
-        <v>46.158111095</v>
+        <v>46.154426415</v>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.002297326</v>
+        <v>-0.002769851</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.006767971</v>
+        <v>-0.006504938</v>
       </c>
       <c r="AE30" s="31" t="n"/>
     </row>
@@ -6815,20 +6815,20 @@
         <v>0.164548037</v>
       </c>
       <c r="Y32" s="24" t="n">
-        <v>0.158890986</v>
+        <v>0.159069055</v>
       </c>
       <c r="Z32" s="25" t="n"/>
       <c r="AA32" s="24" t="n">
-        <v>0.132527158</v>
+        <v>0.132752608</v>
       </c>
       <c r="AB32" s="24" t="n">
-        <v>0.065340678</v>
+        <v>0.065575327</v>
       </c>
       <c r="AC32" s="24" t="n">
-        <v>0.119227732</v>
+        <v>0.119375819</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.119862546</v>
+        <v>0.119800787</v>
       </c>
       <c r="AE32" s="25" t="n"/>
     </row>
@@ -6909,20 +6909,20 @@
         <v>0.111791968</v>
       </c>
       <c r="Y33" s="24" t="n">
-        <v>0.113056699</v>
+        <v>0.113170732</v>
       </c>
       <c r="Z33" s="25" t="n"/>
       <c r="AA33" s="24" t="n">
-        <v>0.098180949</v>
+        <v>0.09835300499999999</v>
       </c>
       <c r="AB33" s="24" t="n">
-        <v>0.049920703</v>
+        <v>0.050115028</v>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>0.09241872299999999</v>
+        <v>0.092545444</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.095201085</v>
+        <v>0.095165836</v>
       </c>
       <c r="AE33" s="25" t="n"/>
     </row>
@@ -7405,11 +7405,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>11470</v>
+        <v>10010</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 11,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 10,700원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1906212641240215</v>
+        <v>0.190618858618165</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.03759308734128065</v>
+        <v>0.03759206047529207</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.02142494935652891</v>
+        <v>0.02143795695451982</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03985281764317002</v>
+        <v>0.0398927915996193</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24168,7 +24168,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27821,7 +27821,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29569,7 +29569,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.98</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="32">
@@ -29579,7 +29579,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="33">
